--- a/public/Excel_template/연간보고서.xlsx
+++ b/public/Excel_template/연간보고서.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ABC_product\product_manage\public\Excel_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CACEF09-21AB-4D10-9357-046C82775822}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D23107B-6037-4CEF-8771-090E6586751A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12135" tabRatio="610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
   <si>
     <t>문서번호</t>
     <phoneticPr fontId="15" type="noConversion"/>
@@ -134,10 +134,6 @@
   </si>
   <si>
     <t>비고</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>25' 내역</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -778,17 +774,125 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="41" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="41" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="21" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -799,21 +903,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -823,112 +912,19 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -1374,50 +1370,50 @@
   <sheetData>
     <row r="1" spans="1:63" ht="8.1" customHeight="1"/>
     <row r="2" spans="1:63" ht="23.1" customHeight="1">
-      <c r="A2" s="44"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
-      <c r="V2" s="45"/>
-      <c r="W2" s="45"/>
-      <c r="X2" s="45"/>
-      <c r="Y2" s="45"/>
-      <c r="Z2" s="46"/>
-      <c r="AA2" s="47" t="s">
+      <c r="A2" s="57"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="58"/>
+      <c r="P2" s="58"/>
+      <c r="Q2" s="58"/>
+      <c r="R2" s="58"/>
+      <c r="S2" s="58"/>
+      <c r="T2" s="58"/>
+      <c r="U2" s="58"/>
+      <c r="V2" s="58"/>
+      <c r="W2" s="58"/>
+      <c r="X2" s="58"/>
+      <c r="Y2" s="58"/>
+      <c r="Z2" s="59"/>
+      <c r="AA2" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="47"/>
-      <c r="AC2" s="48" t="s">
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="AD2" s="49"/>
-      <c r="AE2" s="50"/>
-      <c r="AF2" s="48"/>
-      <c r="AG2" s="49"/>
-      <c r="AH2" s="50"/>
-      <c r="AI2" s="48"/>
-      <c r="AJ2" s="49"/>
-      <c r="AK2" s="50"/>
-      <c r="AL2" s="48"/>
-      <c r="AM2" s="49"/>
-      <c r="AN2" s="50"/>
+      <c r="AD2" s="62"/>
+      <c r="AE2" s="63"/>
+      <c r="AF2" s="61"/>
+      <c r="AG2" s="62"/>
+      <c r="AH2" s="63"/>
+      <c r="AI2" s="61"/>
+      <c r="AJ2" s="62"/>
+      <c r="AK2" s="63"/>
+      <c r="AL2" s="61"/>
+      <c r="AM2" s="62"/>
+      <c r="AN2" s="63"/>
       <c r="AO2" s="6"/>
       <c r="AP2" s="6"/>
       <c r="AQ2" s="6"/>
@@ -1441,46 +1437,46 @@
       <c r="BI2" s="5"/>
     </row>
     <row r="3" spans="1:63" ht="54.95" customHeight="1">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
-      <c r="V3" s="45"/>
-      <c r="W3" s="45"/>
-      <c r="X3" s="45"/>
-      <c r="Y3" s="45"/>
-      <c r="Z3" s="46"/>
-      <c r="AA3" s="47"/>
-      <c r="AB3" s="47"/>
-      <c r="AC3" s="51"/>
-      <c r="AD3" s="52"/>
-      <c r="AE3" s="53"/>
-      <c r="AF3" s="51"/>
-      <c r="AG3" s="52"/>
-      <c r="AH3" s="53"/>
-      <c r="AI3" s="51"/>
-      <c r="AJ3" s="52"/>
-      <c r="AK3" s="53"/>
-      <c r="AL3" s="51"/>
-      <c r="AM3" s="52"/>
-      <c r="AN3" s="53"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="58"/>
+      <c r="O3" s="58"/>
+      <c r="P3" s="58"/>
+      <c r="Q3" s="58"/>
+      <c r="R3" s="58"/>
+      <c r="S3" s="58"/>
+      <c r="T3" s="58"/>
+      <c r="U3" s="58"/>
+      <c r="V3" s="58"/>
+      <c r="W3" s="58"/>
+      <c r="X3" s="58"/>
+      <c r="Y3" s="58"/>
+      <c r="Z3" s="59"/>
+      <c r="AA3" s="60"/>
+      <c r="AB3" s="60"/>
+      <c r="AC3" s="64"/>
+      <c r="AD3" s="65"/>
+      <c r="AE3" s="66"/>
+      <c r="AF3" s="64"/>
+      <c r="AG3" s="65"/>
+      <c r="AH3" s="66"/>
+      <c r="AI3" s="64"/>
+      <c r="AJ3" s="65"/>
+      <c r="AK3" s="66"/>
+      <c r="AL3" s="64"/>
+      <c r="AM3" s="65"/>
+      <c r="AN3" s="66"/>
       <c r="AO3" s="6"/>
       <c r="AP3" s="6"/>
       <c r="AQ3" s="6"/>
@@ -1567,50 +1563,50 @@
       <c r="BI4" s="7"/>
     </row>
     <row r="5" spans="1:63" s="3" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="40"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="40"/>
-      <c r="R5" s="40"/>
-      <c r="S5" s="40"/>
-      <c r="T5" s="41"/>
-      <c r="U5" s="31" t="s">
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
+      <c r="P5" s="71"/>
+      <c r="Q5" s="71"/>
+      <c r="R5" s="71"/>
+      <c r="S5" s="71"/>
+      <c r="T5" s="72"/>
+      <c r="U5" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="V5" s="32"/>
-      <c r="W5" s="32"/>
-      <c r="X5" s="32"/>
-      <c r="Y5" s="32"/>
-      <c r="Z5" s="32"/>
-      <c r="AA5" s="32"/>
-      <c r="AB5" s="33"/>
-      <c r="AC5" s="31"/>
-      <c r="AD5" s="32"/>
-      <c r="AE5" s="32"/>
-      <c r="AF5" s="32"/>
-      <c r="AG5" s="32"/>
-      <c r="AH5" s="32"/>
-      <c r="AI5" s="32"/>
-      <c r="AJ5" s="32"/>
-      <c r="AK5" s="32"/>
-      <c r="AL5" s="32"/>
-      <c r="AM5" s="32"/>
-      <c r="AN5" s="33"/>
+      <c r="V5" s="68"/>
+      <c r="W5" s="68"/>
+      <c r="X5" s="68"/>
+      <c r="Y5" s="68"/>
+      <c r="Z5" s="68"/>
+      <c r="AA5" s="68"/>
+      <c r="AB5" s="69"/>
+      <c r="AC5" s="67"/>
+      <c r="AD5" s="68"/>
+      <c r="AE5" s="68"/>
+      <c r="AF5" s="68"/>
+      <c r="AG5" s="68"/>
+      <c r="AH5" s="68"/>
+      <c r="AI5" s="68"/>
+      <c r="AJ5" s="68"/>
+      <c r="AK5" s="68"/>
+      <c r="AL5" s="68"/>
+      <c r="AM5" s="68"/>
+      <c r="AN5" s="69"/>
       <c r="AO5" s="6"/>
       <c r="AP5" s="6"/>
       <c r="AQ5" s="6"/>
@@ -1636,50 +1632,50 @@
       <c r="BK5" s="22"/>
     </row>
     <row r="6" spans="1:63" s="3" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="32"/>
-      <c r="O6" s="32"/>
-      <c r="P6" s="32"/>
-      <c r="Q6" s="32"/>
-      <c r="R6" s="32"/>
-      <c r="S6" s="32"/>
-      <c r="T6" s="33"/>
-      <c r="U6" s="31" t="s">
+      <c r="B6" s="68"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="68"/>
+      <c r="P6" s="68"/>
+      <c r="Q6" s="68"/>
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="32"/>
-      <c r="W6" s="32"/>
-      <c r="X6" s="32"/>
-      <c r="Y6" s="32"/>
-      <c r="Z6" s="32"/>
-      <c r="AA6" s="32"/>
-      <c r="AB6" s="33"/>
-      <c r="AC6" s="31"/>
-      <c r="AD6" s="32"/>
-      <c r="AE6" s="32"/>
-      <c r="AF6" s="32"/>
-      <c r="AG6" s="32"/>
-      <c r="AH6" s="32"/>
-      <c r="AI6" s="32"/>
-      <c r="AJ6" s="32"/>
-      <c r="AK6" s="32"/>
-      <c r="AL6" s="32"/>
-      <c r="AM6" s="32"/>
-      <c r="AN6" s="33"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="68"/>
+      <c r="Y6" s="68"/>
+      <c r="Z6" s="68"/>
+      <c r="AA6" s="68"/>
+      <c r="AB6" s="69"/>
+      <c r="AC6" s="67"/>
+      <c r="AD6" s="68"/>
+      <c r="AE6" s="68"/>
+      <c r="AF6" s="68"/>
+      <c r="AG6" s="68"/>
+      <c r="AH6" s="68"/>
+      <c r="AI6" s="68"/>
+      <c r="AJ6" s="68"/>
+      <c r="AK6" s="68"/>
+      <c r="AL6" s="68"/>
+      <c r="AM6" s="68"/>
+      <c r="AN6" s="69"/>
       <c r="AO6" s="6"/>
       <c r="AP6" s="6"/>
       <c r="AQ6" s="6"/>
@@ -1770,529 +1766,529 @@
       <c r="BK7" s="22"/>
     </row>
     <row r="8" spans="1:63" s="4" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58" t="s">
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58" t="s">
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="58"/>
-      <c r="K8" s="58"/>
-      <c r="L8" s="58"/>
-      <c r="M8" s="58"/>
-      <c r="N8" s="58"/>
-      <c r="O8" s="58" t="s">
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="38"/>
+      <c r="O8" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="P8" s="58"/>
-      <c r="Q8" s="58"/>
-      <c r="R8" s="58"/>
-      <c r="S8" s="58"/>
-      <c r="T8" s="59"/>
-      <c r="U8" s="77" t="s">
+      <c r="P8" s="38"/>
+      <c r="Q8" s="38"/>
+      <c r="R8" s="38"/>
+      <c r="S8" s="38"/>
+      <c r="T8" s="49"/>
+      <c r="U8" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="V8" s="58"/>
-      <c r="W8" s="58"/>
-      <c r="X8" s="58" t="s">
+      <c r="V8" s="38"/>
+      <c r="W8" s="38"/>
+      <c r="X8" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="Y8" s="58"/>
-      <c r="Z8" s="58"/>
-      <c r="AA8" s="58"/>
-      <c r="AB8" s="58"/>
-      <c r="AC8" s="58" t="s">
+      <c r="Y8" s="38"/>
+      <c r="Z8" s="38"/>
+      <c r="AA8" s="38"/>
+      <c r="AB8" s="38"/>
+      <c r="AC8" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="AD8" s="58"/>
-      <c r="AE8" s="58"/>
-      <c r="AF8" s="58"/>
-      <c r="AG8" s="58"/>
-      <c r="AH8" s="58"/>
-      <c r="AI8" s="58" t="s">
+      <c r="AD8" s="38"/>
+      <c r="AE8" s="38"/>
+      <c r="AF8" s="38"/>
+      <c r="AG8" s="38"/>
+      <c r="AH8" s="38"/>
+      <c r="AI8" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="AJ8" s="58"/>
-      <c r="AK8" s="58"/>
-      <c r="AL8" s="58"/>
-      <c r="AM8" s="58"/>
-      <c r="AN8" s="58"/>
+      <c r="AJ8" s="38"/>
+      <c r="AK8" s="38"/>
+      <c r="AL8" s="38"/>
+      <c r="AM8" s="38"/>
+      <c r="AN8" s="38"/>
       <c r="AO8" s="5"/>
-      <c r="AP8" s="34"/>
-      <c r="AQ8" s="34"/>
-      <c r="AR8" s="34"/>
-      <c r="AS8" s="34"/>
-      <c r="AT8" s="34"/>
-      <c r="AU8" s="34"/>
-      <c r="AV8" s="34"/>
-      <c r="AW8" s="34"/>
+      <c r="AP8" s="50"/>
+      <c r="AQ8" s="50"/>
+      <c r="AR8" s="50"/>
+      <c r="AS8" s="50"/>
+      <c r="AT8" s="50"/>
+      <c r="AU8" s="50"/>
+      <c r="AV8" s="50"/>
+      <c r="AW8" s="50"/>
       <c r="AX8" s="23"/>
       <c r="AY8" s="23"/>
-      <c r="AZ8" s="30"/>
-      <c r="BA8" s="30"/>
-      <c r="BB8" s="30"/>
-      <c r="BC8" s="30"/>
+      <c r="AZ8" s="48"/>
+      <c r="BA8" s="48"/>
+      <c r="BB8" s="48"/>
+      <c r="BC8" s="48"/>
       <c r="BD8" s="24"/>
-      <c r="BE8" s="30"/>
-      <c r="BF8" s="30"/>
-      <c r="BG8" s="30"/>
-      <c r="BH8" s="30"/>
+      <c r="BE8" s="48"/>
+      <c r="BF8" s="48"/>
+      <c r="BG8" s="48"/>
+      <c r="BH8" s="48"/>
       <c r="BI8" s="24"/>
       <c r="BJ8" s="25"/>
       <c r="BK8" s="25"/>
     </row>
     <row r="9" spans="1:63" s="4" customFormat="1" ht="27" customHeight="1" thickTop="1">
-      <c r="A9" s="60" t="s">
+      <c r="A9" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="43"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="43"/>
-      <c r="N9" s="43"/>
-      <c r="O9" s="61"/>
-      <c r="P9" s="61"/>
-      <c r="Q9" s="61"/>
-      <c r="R9" s="61"/>
-      <c r="S9" s="61"/>
-      <c r="T9" s="62"/>
-      <c r="U9" s="76" t="s">
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
+      <c r="K9" s="52"/>
+      <c r="L9" s="52"/>
+      <c r="M9" s="52"/>
+      <c r="N9" s="52"/>
+      <c r="O9" s="51"/>
+      <c r="P9" s="51"/>
+      <c r="Q9" s="51"/>
+      <c r="R9" s="51"/>
+      <c r="S9" s="51"/>
+      <c r="T9" s="54"/>
+      <c r="U9" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="V9" s="60"/>
-      <c r="W9" s="60"/>
-      <c r="X9" s="72"/>
-      <c r="Y9" s="72"/>
-      <c r="Z9" s="72"/>
-      <c r="AA9" s="72"/>
-      <c r="AB9" s="72"/>
-      <c r="AC9" s="43"/>
-      <c r="AD9" s="43"/>
-      <c r="AE9" s="43"/>
-      <c r="AF9" s="43"/>
-      <c r="AG9" s="43"/>
-      <c r="AH9" s="43"/>
-      <c r="AI9" s="61">
+      <c r="V9" s="44"/>
+      <c r="W9" s="44"/>
+      <c r="X9" s="37"/>
+      <c r="Y9" s="37"/>
+      <c r="Z9" s="37"/>
+      <c r="AA9" s="37"/>
+      <c r="AB9" s="37"/>
+      <c r="AC9" s="52"/>
+      <c r="AD9" s="52"/>
+      <c r="AE9" s="52"/>
+      <c r="AF9" s="52"/>
+      <c r="AG9" s="52"/>
+      <c r="AH9" s="52"/>
+      <c r="AI9" s="51">
         <f>O14+X9-AC9</f>
         <v>0</v>
       </c>
-      <c r="AJ9" s="61"/>
-      <c r="AK9" s="61"/>
-      <c r="AL9" s="61"/>
-      <c r="AM9" s="61"/>
-      <c r="AN9" s="61"/>
+      <c r="AJ9" s="51"/>
+      <c r="AK9" s="51"/>
+      <c r="AL9" s="51"/>
+      <c r="AM9" s="51"/>
+      <c r="AN9" s="51"/>
       <c r="AO9" s="5"/>
-      <c r="AP9" s="34"/>
-      <c r="AQ9" s="34"/>
-      <c r="AR9" s="34"/>
-      <c r="AS9" s="34"/>
-      <c r="AT9" s="34"/>
-      <c r="AU9" s="34"/>
-      <c r="AV9" s="34"/>
-      <c r="AW9" s="34"/>
+      <c r="AP9" s="50"/>
+      <c r="AQ9" s="50"/>
+      <c r="AR9" s="50"/>
+      <c r="AS9" s="50"/>
+      <c r="AT9" s="50"/>
+      <c r="AU9" s="50"/>
+      <c r="AV9" s="50"/>
+      <c r="AW9" s="50"/>
       <c r="AX9" s="23"/>
       <c r="AY9" s="23"/>
-      <c r="AZ9" s="30"/>
-      <c r="BA9" s="30"/>
-      <c r="BB9" s="30"/>
-      <c r="BC9" s="30"/>
+      <c r="AZ9" s="48"/>
+      <c r="BA9" s="48"/>
+      <c r="BB9" s="48"/>
+      <c r="BC9" s="48"/>
       <c r="BD9" s="24"/>
-      <c r="BE9" s="30"/>
-      <c r="BF9" s="30"/>
-      <c r="BG9" s="30"/>
-      <c r="BH9" s="30"/>
+      <c r="BE9" s="48"/>
+      <c r="BF9" s="48"/>
+      <c r="BG9" s="48"/>
+      <c r="BH9" s="48"/>
       <c r="BI9" s="24"/>
       <c r="BJ9" s="25"/>
       <c r="BK9" s="25"/>
     </row>
     <row r="10" spans="1:63" s="4" customFormat="1" ht="27" customHeight="1">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="42"/>
-      <c r="O10" s="28">
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="47"/>
+      <c r="L10" s="47"/>
+      <c r="M10" s="47"/>
+      <c r="N10" s="47"/>
+      <c r="O10" s="46">
         <f>O9+D10-I10</f>
         <v>0</v>
       </c>
-      <c r="P10" s="28"/>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="28"/>
-      <c r="S10" s="28"/>
-      <c r="T10" s="56"/>
-      <c r="U10" s="75" t="s">
+      <c r="P10" s="46"/>
+      <c r="Q10" s="46"/>
+      <c r="R10" s="46"/>
+      <c r="S10" s="46"/>
+      <c r="T10" s="53"/>
+      <c r="U10" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="V10" s="27"/>
-      <c r="W10" s="27"/>
-      <c r="X10" s="57"/>
-      <c r="Y10" s="57"/>
-      <c r="Z10" s="57"/>
-      <c r="AA10" s="57"/>
-      <c r="AB10" s="57"/>
-      <c r="AC10" s="42"/>
-      <c r="AD10" s="42"/>
-      <c r="AE10" s="42"/>
-      <c r="AF10" s="42"/>
-      <c r="AG10" s="42"/>
-      <c r="AH10" s="42"/>
-      <c r="AI10" s="28">
+      <c r="V10" s="42"/>
+      <c r="W10" s="42"/>
+      <c r="X10" s="36"/>
+      <c r="Y10" s="36"/>
+      <c r="Z10" s="36"/>
+      <c r="AA10" s="36"/>
+      <c r="AB10" s="36"/>
+      <c r="AC10" s="47"/>
+      <c r="AD10" s="47"/>
+      <c r="AE10" s="47"/>
+      <c r="AF10" s="47"/>
+      <c r="AG10" s="47"/>
+      <c r="AH10" s="47"/>
+      <c r="AI10" s="46">
         <f>AI9+X10-AC10</f>
         <v>0</v>
       </c>
-      <c r="AJ10" s="28"/>
-      <c r="AK10" s="28"/>
-      <c r="AL10" s="28"/>
-      <c r="AM10" s="28"/>
-      <c r="AN10" s="28"/>
+      <c r="AJ10" s="46"/>
+      <c r="AK10" s="46"/>
+      <c r="AL10" s="46"/>
+      <c r="AM10" s="46"/>
+      <c r="AN10" s="46"/>
       <c r="AO10" s="5"/>
-      <c r="AP10" s="34"/>
-      <c r="AQ10" s="34"/>
-      <c r="AR10" s="34"/>
-      <c r="AS10" s="34"/>
-      <c r="AT10" s="34"/>
-      <c r="AU10" s="34"/>
-      <c r="AV10" s="34"/>
-      <c r="AW10" s="34"/>
+      <c r="AP10" s="50"/>
+      <c r="AQ10" s="50"/>
+      <c r="AR10" s="50"/>
+      <c r="AS10" s="50"/>
+      <c r="AT10" s="50"/>
+      <c r="AU10" s="50"/>
+      <c r="AV10" s="50"/>
+      <c r="AW10" s="50"/>
       <c r="AX10" s="23"/>
       <c r="AY10" s="23"/>
-      <c r="AZ10" s="30"/>
-      <c r="BA10" s="30"/>
-      <c r="BB10" s="30"/>
-      <c r="BC10" s="30"/>
+      <c r="AZ10" s="48"/>
+      <c r="BA10" s="48"/>
+      <c r="BB10" s="48"/>
+      <c r="BC10" s="48"/>
       <c r="BD10" s="24"/>
-      <c r="BE10" s="30"/>
-      <c r="BF10" s="30"/>
-      <c r="BG10" s="30"/>
-      <c r="BH10" s="30"/>
+      <c r="BE10" s="48"/>
+      <c r="BF10" s="48"/>
+      <c r="BG10" s="48"/>
+      <c r="BH10" s="48"/>
       <c r="BI10" s="24"/>
       <c r="BJ10" s="25"/>
       <c r="BK10" s="25"/>
     </row>
     <row r="11" spans="1:63" s="4" customFormat="1" ht="27" customHeight="1">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="42"/>
-      <c r="M11" s="42"/>
-      <c r="N11" s="42"/>
-      <c r="O11" s="28">
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="47"/>
+      <c r="L11" s="47"/>
+      <c r="M11" s="47"/>
+      <c r="N11" s="47"/>
+      <c r="O11" s="46">
         <f>O10+D11-I11</f>
         <v>0</v>
       </c>
-      <c r="P11" s="28"/>
-      <c r="Q11" s="28"/>
-      <c r="R11" s="28"/>
-      <c r="S11" s="28"/>
-      <c r="T11" s="56"/>
-      <c r="U11" s="75" t="s">
+      <c r="P11" s="46"/>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="46"/>
+      <c r="S11" s="46"/>
+      <c r="T11" s="53"/>
+      <c r="U11" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="V11" s="27"/>
-      <c r="W11" s="27"/>
-      <c r="X11" s="57"/>
-      <c r="Y11" s="57"/>
-      <c r="Z11" s="57"/>
-      <c r="AA11" s="57"/>
-      <c r="AB11" s="57"/>
-      <c r="AC11" s="42"/>
-      <c r="AD11" s="42"/>
-      <c r="AE11" s="42"/>
-      <c r="AF11" s="42"/>
-      <c r="AG11" s="42"/>
-      <c r="AH11" s="42"/>
-      <c r="AI11" s="28">
+      <c r="V11" s="42"/>
+      <c r="W11" s="42"/>
+      <c r="X11" s="36"/>
+      <c r="Y11" s="36"/>
+      <c r="Z11" s="36"/>
+      <c r="AA11" s="36"/>
+      <c r="AB11" s="36"/>
+      <c r="AC11" s="47"/>
+      <c r="AD11" s="47"/>
+      <c r="AE11" s="47"/>
+      <c r="AF11" s="47"/>
+      <c r="AG11" s="47"/>
+      <c r="AH11" s="47"/>
+      <c r="AI11" s="46">
         <f>AI10+X11-AC11</f>
         <v>0</v>
       </c>
-      <c r="AJ11" s="28"/>
-      <c r="AK11" s="28"/>
-      <c r="AL11" s="28"/>
-      <c r="AM11" s="28"/>
-      <c r="AN11" s="28"/>
+      <c r="AJ11" s="46"/>
+      <c r="AK11" s="46"/>
+      <c r="AL11" s="46"/>
+      <c r="AM11" s="46"/>
+      <c r="AN11" s="46"/>
       <c r="AO11" s="5"/>
-      <c r="AP11" s="34"/>
-      <c r="AQ11" s="34"/>
-      <c r="AR11" s="34"/>
-      <c r="AS11" s="34"/>
-      <c r="AT11" s="34"/>
-      <c r="AU11" s="34"/>
-      <c r="AV11" s="34"/>
-      <c r="AW11" s="34"/>
+      <c r="AP11" s="50"/>
+      <c r="AQ11" s="50"/>
+      <c r="AR11" s="50"/>
+      <c r="AS11" s="50"/>
+      <c r="AT11" s="50"/>
+      <c r="AU11" s="50"/>
+      <c r="AV11" s="50"/>
+      <c r="AW11" s="50"/>
       <c r="AX11" s="23"/>
       <c r="AY11" s="23"/>
-      <c r="AZ11" s="30"/>
-      <c r="BA11" s="30"/>
-      <c r="BB11" s="30"/>
-      <c r="BC11" s="30"/>
+      <c r="AZ11" s="48"/>
+      <c r="BA11" s="48"/>
+      <c r="BB11" s="48"/>
+      <c r="BC11" s="48"/>
       <c r="BD11" s="24"/>
-      <c r="BE11" s="30"/>
-      <c r="BF11" s="30"/>
-      <c r="BG11" s="30"/>
-      <c r="BH11" s="30"/>
+      <c r="BE11" s="48"/>
+      <c r="BF11" s="48"/>
+      <c r="BG11" s="48"/>
+      <c r="BH11" s="48"/>
       <c r="BI11" s="24"/>
       <c r="BJ11" s="25"/>
       <c r="BK11" s="25"/>
     </row>
     <row r="12" spans="1:63" s="4" customFormat="1" ht="27" customHeight="1">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
-      <c r="K12" s="42"/>
-      <c r="L12" s="42"/>
-      <c r="M12" s="42"/>
-      <c r="N12" s="42"/>
-      <c r="O12" s="28">
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="47"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="46">
         <f>O11+D12-I12</f>
         <v>0</v>
       </c>
-      <c r="P12" s="28"/>
-      <c r="Q12" s="28"/>
-      <c r="R12" s="28"/>
-      <c r="S12" s="28"/>
-      <c r="T12" s="56"/>
-      <c r="U12" s="75" t="s">
+      <c r="P12" s="46"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="46"/>
+      <c r="S12" s="46"/>
+      <c r="T12" s="53"/>
+      <c r="U12" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="V12" s="27"/>
-      <c r="W12" s="27"/>
-      <c r="X12" s="57"/>
-      <c r="Y12" s="57"/>
-      <c r="Z12" s="57"/>
-      <c r="AA12" s="57"/>
-      <c r="AB12" s="57"/>
-      <c r="AC12" s="42"/>
-      <c r="AD12" s="42"/>
-      <c r="AE12" s="42"/>
-      <c r="AF12" s="42"/>
-      <c r="AG12" s="42"/>
-      <c r="AH12" s="42"/>
-      <c r="AI12" s="28">
+      <c r="V12" s="42"/>
+      <c r="W12" s="42"/>
+      <c r="X12" s="36"/>
+      <c r="Y12" s="36"/>
+      <c r="Z12" s="36"/>
+      <c r="AA12" s="36"/>
+      <c r="AB12" s="36"/>
+      <c r="AC12" s="47"/>
+      <c r="AD12" s="47"/>
+      <c r="AE12" s="47"/>
+      <c r="AF12" s="47"/>
+      <c r="AG12" s="47"/>
+      <c r="AH12" s="47"/>
+      <c r="AI12" s="46">
         <f>AI11+X12-AC12</f>
         <v>0</v>
       </c>
-      <c r="AJ12" s="28"/>
-      <c r="AK12" s="28"/>
-      <c r="AL12" s="28"/>
-      <c r="AM12" s="28"/>
-      <c r="AN12" s="28"/>
+      <c r="AJ12" s="46"/>
+      <c r="AK12" s="46"/>
+      <c r="AL12" s="46"/>
+      <c r="AM12" s="46"/>
+      <c r="AN12" s="46"/>
       <c r="AO12" s="5"/>
-      <c r="AP12" s="34"/>
-      <c r="AQ12" s="34"/>
-      <c r="AR12" s="34"/>
-      <c r="AS12" s="34"/>
-      <c r="AT12" s="34"/>
-      <c r="AU12" s="34"/>
-      <c r="AV12" s="34"/>
-      <c r="AW12" s="34"/>
+      <c r="AP12" s="50"/>
+      <c r="AQ12" s="50"/>
+      <c r="AR12" s="50"/>
+      <c r="AS12" s="50"/>
+      <c r="AT12" s="50"/>
+      <c r="AU12" s="50"/>
+      <c r="AV12" s="50"/>
+      <c r="AW12" s="50"/>
       <c r="AX12" s="23"/>
       <c r="AY12" s="23"/>
-      <c r="AZ12" s="30"/>
-      <c r="BA12" s="30"/>
-      <c r="BB12" s="30"/>
-      <c r="BC12" s="30"/>
+      <c r="AZ12" s="48"/>
+      <c r="BA12" s="48"/>
+      <c r="BB12" s="48"/>
+      <c r="BC12" s="48"/>
       <c r="BD12" s="24"/>
-      <c r="BE12" s="30"/>
-      <c r="BF12" s="30"/>
-      <c r="BG12" s="30"/>
-      <c r="BH12" s="30"/>
+      <c r="BE12" s="48"/>
+      <c r="BF12" s="48"/>
+      <c r="BG12" s="48"/>
+      <c r="BH12" s="48"/>
       <c r="BI12" s="24"/>
       <c r="BJ12" s="25"/>
       <c r="BK12" s="25"/>
     </row>
     <row r="13" spans="1:63" s="4" customFormat="1" ht="27" customHeight="1">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="42"/>
-      <c r="K13" s="42"/>
-      <c r="L13" s="42"/>
-      <c r="M13" s="42"/>
-      <c r="N13" s="42"/>
-      <c r="O13" s="28">
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="47"/>
+      <c r="L13" s="47"/>
+      <c r="M13" s="47"/>
+      <c r="N13" s="47"/>
+      <c r="O13" s="46">
         <f>O12+D13-I13</f>
         <v>0</v>
       </c>
-      <c r="P13" s="28"/>
-      <c r="Q13" s="28"/>
-      <c r="R13" s="28"/>
-      <c r="S13" s="28"/>
-      <c r="T13" s="56"/>
-      <c r="U13" s="75" t="s">
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="46"/>
+      <c r="S13" s="46"/>
+      <c r="T13" s="53"/>
+      <c r="U13" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="V13" s="27"/>
-      <c r="W13" s="27"/>
-      <c r="X13" s="57"/>
-      <c r="Y13" s="57"/>
-      <c r="Z13" s="57"/>
-      <c r="AA13" s="57"/>
-      <c r="AB13" s="57"/>
-      <c r="AC13" s="42"/>
-      <c r="AD13" s="42"/>
-      <c r="AE13" s="42"/>
-      <c r="AF13" s="42"/>
-      <c r="AG13" s="42"/>
-      <c r="AH13" s="42"/>
-      <c r="AI13" s="28">
+      <c r="V13" s="42"/>
+      <c r="W13" s="42"/>
+      <c r="X13" s="36"/>
+      <c r="Y13" s="36"/>
+      <c r="Z13" s="36"/>
+      <c r="AA13" s="36"/>
+      <c r="AB13" s="36"/>
+      <c r="AC13" s="47"/>
+      <c r="AD13" s="47"/>
+      <c r="AE13" s="47"/>
+      <c r="AF13" s="47"/>
+      <c r="AG13" s="47"/>
+      <c r="AH13" s="47"/>
+      <c r="AI13" s="46">
         <f>AI12+X13-AC13</f>
         <v>0</v>
       </c>
-      <c r="AJ13" s="28"/>
-      <c r="AK13" s="28"/>
-      <c r="AL13" s="28"/>
-      <c r="AM13" s="28"/>
-      <c r="AN13" s="28"/>
+      <c r="AJ13" s="46"/>
+      <c r="AK13" s="46"/>
+      <c r="AL13" s="46"/>
+      <c r="AM13" s="46"/>
+      <c r="AN13" s="46"/>
       <c r="AO13" s="5"/>
-      <c r="AP13" s="34"/>
-      <c r="AQ13" s="34"/>
-      <c r="AR13" s="34"/>
-      <c r="AS13" s="34"/>
-      <c r="AT13" s="34"/>
-      <c r="AU13" s="34"/>
-      <c r="AV13" s="34"/>
-      <c r="AW13" s="34"/>
+      <c r="AP13" s="50"/>
+      <c r="AQ13" s="50"/>
+      <c r="AR13" s="50"/>
+      <c r="AS13" s="50"/>
+      <c r="AT13" s="50"/>
+      <c r="AU13" s="50"/>
+      <c r="AV13" s="50"/>
+      <c r="AW13" s="50"/>
       <c r="AX13" s="23"/>
       <c r="AY13" s="23"/>
-      <c r="AZ13" s="30"/>
-      <c r="BA13" s="30"/>
-      <c r="BB13" s="30"/>
-      <c r="BC13" s="30"/>
+      <c r="AZ13" s="48"/>
+      <c r="BA13" s="48"/>
+      <c r="BB13" s="48"/>
+      <c r="BC13" s="48"/>
       <c r="BD13" s="24"/>
-      <c r="BE13" s="30"/>
-      <c r="BF13" s="30"/>
-      <c r="BG13" s="30"/>
-      <c r="BH13" s="30"/>
+      <c r="BE13" s="48"/>
+      <c r="BF13" s="48"/>
+      <c r="BG13" s="48"/>
+      <c r="BH13" s="48"/>
       <c r="BI13" s="24"/>
       <c r="BJ13" s="25"/>
       <c r="BK13" s="25"/>
     </row>
     <row r="14" spans="1:63" s="4" customFormat="1" ht="27" customHeight="1">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="42"/>
-      <c r="L14" s="42"/>
-      <c r="M14" s="42"/>
-      <c r="N14" s="42"/>
-      <c r="O14" s="28">
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="47"/>
+      <c r="N14" s="47"/>
+      <c r="O14" s="46">
         <f>O13+D14-I14</f>
         <v>0</v>
       </c>
-      <c r="P14" s="28"/>
-      <c r="Q14" s="28"/>
-      <c r="R14" s="28"/>
-      <c r="S14" s="28"/>
-      <c r="T14" s="56"/>
-      <c r="U14" s="75" t="s">
+      <c r="P14" s="46"/>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="46"/>
+      <c r="S14" s="46"/>
+      <c r="T14" s="53"/>
+      <c r="U14" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="V14" s="27"/>
-      <c r="W14" s="27"/>
-      <c r="X14" s="57"/>
-      <c r="Y14" s="57"/>
-      <c r="Z14" s="57"/>
-      <c r="AA14" s="57"/>
-      <c r="AB14" s="57"/>
-      <c r="AC14" s="42"/>
-      <c r="AD14" s="42"/>
-      <c r="AE14" s="42"/>
-      <c r="AF14" s="42"/>
-      <c r="AG14" s="42"/>
-      <c r="AH14" s="42"/>
-      <c r="AI14" s="28">
+      <c r="V14" s="42"/>
+      <c r="W14" s="42"/>
+      <c r="X14" s="36"/>
+      <c r="Y14" s="36"/>
+      <c r="Z14" s="36"/>
+      <c r="AA14" s="36"/>
+      <c r="AB14" s="36"/>
+      <c r="AC14" s="47"/>
+      <c r="AD14" s="47"/>
+      <c r="AE14" s="47"/>
+      <c r="AF14" s="47"/>
+      <c r="AG14" s="47"/>
+      <c r="AH14" s="47"/>
+      <c r="AI14" s="46">
         <f>AI13+X14-AC14</f>
         <v>0</v>
       </c>
-      <c r="AJ14" s="28"/>
-      <c r="AK14" s="28"/>
-      <c r="AL14" s="28"/>
-      <c r="AM14" s="28"/>
-      <c r="AN14" s="28"/>
+      <c r="AJ14" s="46"/>
+      <c r="AK14" s="46"/>
+      <c r="AL14" s="46"/>
+      <c r="AM14" s="46"/>
+      <c r="AN14" s="46"/>
       <c r="AO14" s="5"/>
-      <c r="AP14" s="34"/>
-      <c r="AQ14" s="34"/>
-      <c r="AR14" s="34"/>
-      <c r="AS14" s="34"/>
-      <c r="AT14" s="34"/>
-      <c r="AU14" s="34"/>
-      <c r="AV14" s="34"/>
-      <c r="AW14" s="34"/>
+      <c r="AP14" s="50"/>
+      <c r="AQ14" s="50"/>
+      <c r="AR14" s="50"/>
+      <c r="AS14" s="50"/>
+      <c r="AT14" s="50"/>
+      <c r="AU14" s="50"/>
+      <c r="AV14" s="50"/>
+      <c r="AW14" s="50"/>
       <c r="AX14" s="23"/>
       <c r="AY14" s="23"/>
-      <c r="AZ14" s="30"/>
-      <c r="BA14" s="30"/>
-      <c r="BB14" s="30"/>
-      <c r="BC14" s="30"/>
+      <c r="AZ14" s="48"/>
+      <c r="BA14" s="48"/>
+      <c r="BB14" s="48"/>
+      <c r="BC14" s="48"/>
       <c r="BD14" s="24"/>
-      <c r="BE14" s="30"/>
-      <c r="BF14" s="30"/>
-      <c r="BG14" s="30"/>
-      <c r="BH14" s="30"/>
+      <c r="BE14" s="48"/>
+      <c r="BF14" s="48"/>
+      <c r="BG14" s="48"/>
+      <c r="BH14" s="48"/>
       <c r="BI14" s="24"/>
       <c r="BJ14" s="25"/>
       <c r="BK14" s="25"/>
@@ -2318,34 +2314,32 @@
       <c r="R15" s="19"/>
       <c r="S15" s="19"/>
       <c r="T15" s="19"/>
-      <c r="U15" s="73" t="s">
-        <v>28</v>
-      </c>
-      <c r="V15" s="74"/>
-      <c r="W15" s="74"/>
-      <c r="X15" s="38">
+      <c r="U15" s="39"/>
+      <c r="V15" s="40"/>
+      <c r="W15" s="40"/>
+      <c r="X15" s="77">
         <f>SUM(D9:H14,X9:AB14)</f>
         <v>0</v>
       </c>
-      <c r="Y15" s="38"/>
-      <c r="Z15" s="38"/>
-      <c r="AA15" s="38"/>
-      <c r="AB15" s="38"/>
-      <c r="AC15" s="36">
+      <c r="Y15" s="77"/>
+      <c r="Z15" s="77"/>
+      <c r="AA15" s="77"/>
+      <c r="AB15" s="77"/>
+      <c r="AC15" s="75">
         <f>SUM(I9:N14,AC9:AH14)</f>
         <v>0</v>
       </c>
-      <c r="AD15" s="36"/>
-      <c r="AE15" s="36"/>
-      <c r="AF15" s="36"/>
-      <c r="AG15" s="36"/>
-      <c r="AH15" s="36"/>
-      <c r="AI15" s="37"/>
-      <c r="AJ15" s="37"/>
-      <c r="AK15" s="37"/>
-      <c r="AL15" s="37"/>
-      <c r="AM15" s="37"/>
-      <c r="AN15" s="37"/>
+      <c r="AD15" s="75"/>
+      <c r="AE15" s="75"/>
+      <c r="AF15" s="75"/>
+      <c r="AG15" s="75"/>
+      <c r="AH15" s="75"/>
+      <c r="AI15" s="76"/>
+      <c r="AJ15" s="76"/>
+      <c r="AK15" s="76"/>
+      <c r="AL15" s="76"/>
+      <c r="AM15" s="76"/>
+      <c r="AN15" s="76"/>
       <c r="AO15" s="5"/>
       <c r="AP15" s="15"/>
       <c r="AQ15" s="15"/>
@@ -2397,7 +2391,7 @@
     </row>
     <row r="17" spans="1:63" ht="24.95" customHeight="1">
       <c r="A17" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
@@ -2462,122 +2456,178 @@
       <c r="BK17" s="26"/>
     </row>
     <row r="18" spans="1:63" ht="27" customHeight="1">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="35" t="s">
+      <c r="B18" s="73"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35" t="s">
+      <c r="F18" s="74"/>
+      <c r="G18" s="74"/>
+      <c r="H18" s="74"/>
+      <c r="I18" s="74"/>
+      <c r="J18" s="74"/>
+      <c r="K18" s="74"/>
+      <c r="L18" s="74"/>
+      <c r="M18" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
-      <c r="R18" s="35"/>
-      <c r="S18" s="35"/>
-      <c r="T18" s="35"/>
-      <c r="U18" s="29" t="s">
+      <c r="N18" s="74"/>
+      <c r="O18" s="74"/>
+      <c r="P18" s="74"/>
+      <c r="Q18" s="74"/>
+      <c r="R18" s="74"/>
+      <c r="S18" s="74"/>
+      <c r="T18" s="74"/>
+      <c r="U18" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="V18" s="29"/>
-      <c r="W18" s="29"/>
-      <c r="X18" s="29"/>
-      <c r="Y18" s="29"/>
-      <c r="Z18" s="29"/>
-      <c r="AA18" s="29"/>
-      <c r="AB18" s="29"/>
-      <c r="AC18" s="66" t="s">
+      <c r="V18" s="73"/>
+      <c r="W18" s="73"/>
+      <c r="X18" s="73"/>
+      <c r="Y18" s="73"/>
+      <c r="Z18" s="73"/>
+      <c r="AA18" s="73"/>
+      <c r="AB18" s="73"/>
+      <c r="AC18" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="AD18" s="67"/>
-      <c r="AE18" s="67"/>
-      <c r="AF18" s="67"/>
-      <c r="AG18" s="67"/>
-      <c r="AH18" s="68"/>
-      <c r="AI18" s="66" t="s">
+      <c r="AD18" s="31"/>
+      <c r="AE18" s="31"/>
+      <c r="AF18" s="31"/>
+      <c r="AG18" s="31"/>
+      <c r="AH18" s="32"/>
+      <c r="AI18" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="AJ18" s="67"/>
-      <c r="AK18" s="67"/>
-      <c r="AL18" s="67"/>
-      <c r="AM18" s="67"/>
-      <c r="AN18" s="68"/>
+      <c r="AJ18" s="31"/>
+      <c r="AK18" s="31"/>
+      <c r="AL18" s="31"/>
+      <c r="AM18" s="31"/>
+      <c r="AN18" s="32"/>
     </row>
     <row r="19" spans="1:63" ht="27" customHeight="1">
-      <c r="A19" s="27"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="28"/>
-      <c r="O19" s="28"/>
-      <c r="P19" s="28"/>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="28"/>
-      <c r="T19" s="28"/>
-      <c r="U19" s="28"/>
-      <c r="V19" s="27"/>
-      <c r="W19" s="27"/>
-      <c r="X19" s="27"/>
-      <c r="Y19" s="27"/>
-      <c r="Z19" s="27"/>
-      <c r="AA19" s="27"/>
-      <c r="AB19" s="27"/>
-      <c r="AC19" s="63"/>
-      <c r="AD19" s="64"/>
-      <c r="AE19" s="64"/>
-      <c r="AF19" s="64"/>
-      <c r="AG19" s="64"/>
-      <c r="AH19" s="65"/>
-      <c r="AI19" s="69"/>
-      <c r="AJ19" s="70"/>
-      <c r="AK19" s="70"/>
-      <c r="AL19" s="70"/>
-      <c r="AM19" s="70"/>
-      <c r="AN19" s="71"/>
+      <c r="A19" s="42"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="46"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="46"/>
+      <c r="M19" s="46"/>
+      <c r="N19" s="46"/>
+      <c r="O19" s="46"/>
+      <c r="P19" s="46"/>
+      <c r="Q19" s="46"/>
+      <c r="R19" s="46"/>
+      <c r="S19" s="46"/>
+      <c r="T19" s="46"/>
+      <c r="U19" s="46"/>
+      <c r="V19" s="42"/>
+      <c r="W19" s="42"/>
+      <c r="X19" s="42"/>
+      <c r="Y19" s="42"/>
+      <c r="Z19" s="42"/>
+      <c r="AA19" s="42"/>
+      <c r="AB19" s="42"/>
+      <c r="AC19" s="27"/>
+      <c r="AD19" s="28"/>
+      <c r="AE19" s="28"/>
+      <c r="AF19" s="28"/>
+      <c r="AG19" s="28"/>
+      <c r="AH19" s="29"/>
+      <c r="AI19" s="33"/>
+      <c r="AJ19" s="34"/>
+      <c r="AK19" s="34"/>
+      <c r="AL19" s="34"/>
+      <c r="AM19" s="34"/>
+      <c r="AN19" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="118">
-    <mergeCell ref="AC19:AH19"/>
-    <mergeCell ref="AC18:AH18"/>
-    <mergeCell ref="AI19:AN19"/>
-    <mergeCell ref="AI18:AN18"/>
-    <mergeCell ref="X11:AB11"/>
-    <mergeCell ref="X10:AB10"/>
-    <mergeCell ref="X9:AB9"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="U15:W15"/>
-    <mergeCell ref="U14:W14"/>
-    <mergeCell ref="U13:W13"/>
-    <mergeCell ref="U12:W12"/>
-    <mergeCell ref="U11:W11"/>
-    <mergeCell ref="U10:W10"/>
-    <mergeCell ref="U9:W9"/>
-    <mergeCell ref="U8:W8"/>
-    <mergeCell ref="AI12:AN12"/>
-    <mergeCell ref="AI11:AN11"/>
-    <mergeCell ref="AC14:AH14"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="AI14:AN14"/>
+    <mergeCell ref="AI13:AN13"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="BE9:BH9"/>
+    <mergeCell ref="U5:AB5"/>
+    <mergeCell ref="U6:AB6"/>
+    <mergeCell ref="AP9:AS9"/>
+    <mergeCell ref="AT9:AW9"/>
+    <mergeCell ref="U19:AB19"/>
+    <mergeCell ref="M19:T19"/>
+    <mergeCell ref="E19:L19"/>
+    <mergeCell ref="E18:L18"/>
+    <mergeCell ref="M18:T18"/>
+    <mergeCell ref="U18:AB18"/>
+    <mergeCell ref="AC15:AH15"/>
+    <mergeCell ref="AI15:AN15"/>
+    <mergeCell ref="X15:AB15"/>
+    <mergeCell ref="AT11:AW11"/>
+    <mergeCell ref="AZ11:BC11"/>
+    <mergeCell ref="BE11:BH11"/>
+    <mergeCell ref="AP10:AS10"/>
+    <mergeCell ref="AT10:AW10"/>
+    <mergeCell ref="BE10:BH10"/>
+    <mergeCell ref="AP14:AS14"/>
+    <mergeCell ref="AT14:AW14"/>
+    <mergeCell ref="AZ14:BC14"/>
+    <mergeCell ref="BE14:BH14"/>
+    <mergeCell ref="AP13:AS13"/>
+    <mergeCell ref="AT13:AW13"/>
+    <mergeCell ref="AZ13:BC13"/>
+    <mergeCell ref="BE13:BH13"/>
+    <mergeCell ref="AP12:AS12"/>
+    <mergeCell ref="AT12:AW12"/>
+    <mergeCell ref="AZ12:BC12"/>
+    <mergeCell ref="BE12:BH12"/>
+    <mergeCell ref="AP11:AS11"/>
+    <mergeCell ref="AC6:AN6"/>
+    <mergeCell ref="AC5:AN5"/>
+    <mergeCell ref="I5:T5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="I6:T6"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="AT8:AW8"/>
+    <mergeCell ref="AZ8:BC8"/>
+    <mergeCell ref="AZ10:BC10"/>
+    <mergeCell ref="I10:N10"/>
+    <mergeCell ref="I9:N9"/>
+    <mergeCell ref="A2:Z3"/>
+    <mergeCell ref="AA2:AB3"/>
+    <mergeCell ref="AC2:AE2"/>
+    <mergeCell ref="AF2:AH2"/>
+    <mergeCell ref="AI2:AK2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="AC3:AE3"/>
+    <mergeCell ref="AF3:AH3"/>
+    <mergeCell ref="AI3:AK3"/>
+    <mergeCell ref="AL3:AN3"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="AZ9:BC9"/>
+    <mergeCell ref="O14:T14"/>
+    <mergeCell ref="O13:T13"/>
+    <mergeCell ref="O12:T12"/>
+    <mergeCell ref="X14:AB14"/>
+    <mergeCell ref="X13:AB13"/>
+    <mergeCell ref="X12:AB12"/>
+    <mergeCell ref="I14:N14"/>
+    <mergeCell ref="I13:N13"/>
+    <mergeCell ref="I12:N12"/>
     <mergeCell ref="BE8:BH8"/>
     <mergeCell ref="I8:N8"/>
     <mergeCell ref="AC8:AH8"/>
@@ -2602,81 +2652,25 @@
     <mergeCell ref="O10:T10"/>
     <mergeCell ref="O9:T9"/>
     <mergeCell ref="I11:N11"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="AZ9:BC9"/>
-    <mergeCell ref="O14:T14"/>
-    <mergeCell ref="O13:T13"/>
-    <mergeCell ref="O12:T12"/>
-    <mergeCell ref="X14:AB14"/>
-    <mergeCell ref="X13:AB13"/>
-    <mergeCell ref="X12:AB12"/>
-    <mergeCell ref="I14:N14"/>
-    <mergeCell ref="I13:N13"/>
-    <mergeCell ref="I12:N12"/>
-    <mergeCell ref="A2:Z3"/>
-    <mergeCell ref="AA2:AB3"/>
-    <mergeCell ref="AC2:AE2"/>
-    <mergeCell ref="AF2:AH2"/>
-    <mergeCell ref="AI2:AK2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="AC3:AE3"/>
-    <mergeCell ref="AF3:AH3"/>
-    <mergeCell ref="AI3:AK3"/>
-    <mergeCell ref="AL3:AN3"/>
-    <mergeCell ref="AC6:AN6"/>
-    <mergeCell ref="AC5:AN5"/>
-    <mergeCell ref="I5:T5"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="I6:T6"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="AT8:AW8"/>
-    <mergeCell ref="AZ8:BC8"/>
-    <mergeCell ref="AZ10:BC10"/>
-    <mergeCell ref="I10:N10"/>
-    <mergeCell ref="I9:N9"/>
-    <mergeCell ref="BE10:BH10"/>
-    <mergeCell ref="AP14:AS14"/>
-    <mergeCell ref="AT14:AW14"/>
-    <mergeCell ref="AZ14:BC14"/>
-    <mergeCell ref="BE14:BH14"/>
-    <mergeCell ref="AP13:AS13"/>
-    <mergeCell ref="AT13:AW13"/>
-    <mergeCell ref="AZ13:BC13"/>
-    <mergeCell ref="BE13:BH13"/>
-    <mergeCell ref="AP12:AS12"/>
-    <mergeCell ref="AT12:AW12"/>
-    <mergeCell ref="AZ12:BC12"/>
-    <mergeCell ref="BE12:BH12"/>
-    <mergeCell ref="AP11:AS11"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="AI14:AN14"/>
-    <mergeCell ref="AI13:AN13"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="BE9:BH9"/>
-    <mergeCell ref="U5:AB5"/>
-    <mergeCell ref="U6:AB6"/>
-    <mergeCell ref="AP9:AS9"/>
-    <mergeCell ref="AT9:AW9"/>
-    <mergeCell ref="U19:AB19"/>
-    <mergeCell ref="M19:T19"/>
-    <mergeCell ref="E19:L19"/>
-    <mergeCell ref="E18:L18"/>
-    <mergeCell ref="M18:T18"/>
-    <mergeCell ref="U18:AB18"/>
-    <mergeCell ref="AC15:AH15"/>
-    <mergeCell ref="AI15:AN15"/>
-    <mergeCell ref="X15:AB15"/>
-    <mergeCell ref="AT11:AW11"/>
-    <mergeCell ref="AZ11:BC11"/>
-    <mergeCell ref="BE11:BH11"/>
-    <mergeCell ref="AP10:AS10"/>
-    <mergeCell ref="AT10:AW10"/>
+    <mergeCell ref="AC19:AH19"/>
+    <mergeCell ref="AC18:AH18"/>
+    <mergeCell ref="AI19:AN19"/>
+    <mergeCell ref="AI18:AN18"/>
+    <mergeCell ref="X11:AB11"/>
+    <mergeCell ref="X10:AB10"/>
+    <mergeCell ref="X9:AB9"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="U15:W15"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="U13:W13"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="U11:W11"/>
+    <mergeCell ref="U10:W10"/>
+    <mergeCell ref="U9:W9"/>
+    <mergeCell ref="U8:W8"/>
+    <mergeCell ref="AI12:AN12"/>
+    <mergeCell ref="AI11:AN11"/>
+    <mergeCell ref="AC14:AH14"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.78740157480314965" right="0.59055118110236227" top="0.98425196850393704" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/public/Excel_template/연간보고서.xlsx
+++ b/public/Excel_template/연간보고서.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ABC_product\product_manage\public\Excel_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D23107B-6037-4CEF-8771-090E6586751A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73EDCB70-67E8-429B-B43D-1B3B937278B7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12135" tabRatio="610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -774,6 +774,114 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="21" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="176" fontId="10" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1" shrinkToFit="1"/>
     </xf>
@@ -801,15 +909,9 @@
     <xf numFmtId="176" fontId="10" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="41" fontId="20" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -819,112 +921,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -1370,50 +1370,50 @@
   <sheetData>
     <row r="1" spans="1:63" ht="8.1" customHeight="1"/>
     <row r="2" spans="1:63" ht="23.1" customHeight="1">
-      <c r="A2" s="57"/>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="58"/>
-      <c r="W2" s="58"/>
-      <c r="X2" s="58"/>
-      <c r="Y2" s="58"/>
-      <c r="Z2" s="59"/>
-      <c r="AA2" s="60" t="s">
+      <c r="A2" s="44"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="45"/>
+      <c r="V2" s="45"/>
+      <c r="W2" s="45"/>
+      <c r="X2" s="45"/>
+      <c r="Y2" s="45"/>
+      <c r="Z2" s="46"/>
+      <c r="AA2" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="60"/>
-      <c r="AC2" s="61" t="s">
+      <c r="AB2" s="47"/>
+      <c r="AC2" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="AD2" s="62"/>
-      <c r="AE2" s="63"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="62"/>
-      <c r="AH2" s="63"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="62"/>
-      <c r="AK2" s="63"/>
-      <c r="AL2" s="61"/>
-      <c r="AM2" s="62"/>
-      <c r="AN2" s="63"/>
+      <c r="AD2" s="49"/>
+      <c r="AE2" s="50"/>
+      <c r="AF2" s="48"/>
+      <c r="AG2" s="49"/>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="48"/>
+      <c r="AJ2" s="49"/>
+      <c r="AK2" s="50"/>
+      <c r="AL2" s="48"/>
+      <c r="AM2" s="49"/>
+      <c r="AN2" s="50"/>
       <c r="AO2" s="6"/>
       <c r="AP2" s="6"/>
       <c r="AQ2" s="6"/>
@@ -1437,46 +1437,46 @@
       <c r="BI2" s="5"/>
     </row>
     <row r="3" spans="1:63" ht="54.95" customHeight="1">
-      <c r="A3" s="58"/>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
-      <c r="L3" s="58"/>
-      <c r="M3" s="58"/>
-      <c r="N3" s="58"/>
-      <c r="O3" s="58"/>
-      <c r="P3" s="58"/>
-      <c r="Q3" s="58"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="58"/>
-      <c r="T3" s="58"/>
-      <c r="U3" s="58"/>
-      <c r="V3" s="58"/>
-      <c r="W3" s="58"/>
-      <c r="X3" s="58"/>
-      <c r="Y3" s="58"/>
-      <c r="Z3" s="59"/>
-      <c r="AA3" s="60"/>
-      <c r="AB3" s="60"/>
-      <c r="AC3" s="64"/>
-      <c r="AD3" s="65"/>
-      <c r="AE3" s="66"/>
-      <c r="AF3" s="64"/>
-      <c r="AG3" s="65"/>
-      <c r="AH3" s="66"/>
-      <c r="AI3" s="64"/>
-      <c r="AJ3" s="65"/>
-      <c r="AK3" s="66"/>
-      <c r="AL3" s="64"/>
-      <c r="AM3" s="65"/>
-      <c r="AN3" s="66"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="45"/>
+      <c r="Q3" s="45"/>
+      <c r="R3" s="45"/>
+      <c r="S3" s="45"/>
+      <c r="T3" s="45"/>
+      <c r="U3" s="45"/>
+      <c r="V3" s="45"/>
+      <c r="W3" s="45"/>
+      <c r="X3" s="45"/>
+      <c r="Y3" s="45"/>
+      <c r="Z3" s="46"/>
+      <c r="AA3" s="47"/>
+      <c r="AB3" s="47"/>
+      <c r="AC3" s="51"/>
+      <c r="AD3" s="52"/>
+      <c r="AE3" s="53"/>
+      <c r="AF3" s="51"/>
+      <c r="AG3" s="52"/>
+      <c r="AH3" s="53"/>
+      <c r="AI3" s="51"/>
+      <c r="AJ3" s="52"/>
+      <c r="AK3" s="53"/>
+      <c r="AL3" s="51"/>
+      <c r="AM3" s="52"/>
+      <c r="AN3" s="53"/>
       <c r="AO3" s="6"/>
       <c r="AP3" s="6"/>
       <c r="AQ3" s="6"/>
@@ -1563,50 +1563,50 @@
       <c r="BI4" s="7"/>
     </row>
     <row r="5" spans="1:63" s="3" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71"/>
-      <c r="O5" s="71"/>
-      <c r="P5" s="71"/>
-      <c r="Q5" s="71"/>
-      <c r="R5" s="71"/>
-      <c r="S5" s="71"/>
-      <c r="T5" s="72"/>
-      <c r="U5" s="67" t="s">
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="40"/>
+      <c r="Q5" s="40"/>
+      <c r="R5" s="40"/>
+      <c r="S5" s="40"/>
+      <c r="T5" s="41"/>
+      <c r="U5" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="V5" s="68"/>
-      <c r="W5" s="68"/>
-      <c r="X5" s="68"/>
-      <c r="Y5" s="68"/>
-      <c r="Z5" s="68"/>
-      <c r="AA5" s="68"/>
-      <c r="AB5" s="69"/>
-      <c r="AC5" s="67"/>
-      <c r="AD5" s="68"/>
-      <c r="AE5" s="68"/>
-      <c r="AF5" s="68"/>
-      <c r="AG5" s="68"/>
-      <c r="AH5" s="68"/>
-      <c r="AI5" s="68"/>
-      <c r="AJ5" s="68"/>
-      <c r="AK5" s="68"/>
-      <c r="AL5" s="68"/>
-      <c r="AM5" s="68"/>
-      <c r="AN5" s="69"/>
+      <c r="V5" s="32"/>
+      <c r="W5" s="32"/>
+      <c r="X5" s="32"/>
+      <c r="Y5" s="32"/>
+      <c r="Z5" s="32"/>
+      <c r="AA5" s="32"/>
+      <c r="AB5" s="33"/>
+      <c r="AC5" s="31"/>
+      <c r="AD5" s="32"/>
+      <c r="AE5" s="32"/>
+      <c r="AF5" s="32"/>
+      <c r="AG5" s="32"/>
+      <c r="AH5" s="32"/>
+      <c r="AI5" s="32"/>
+      <c r="AJ5" s="32"/>
+      <c r="AK5" s="32"/>
+      <c r="AL5" s="32"/>
+      <c r="AM5" s="32"/>
+      <c r="AN5" s="33"/>
       <c r="AO5" s="6"/>
       <c r="AP5" s="6"/>
       <c r="AQ5" s="6"/>
@@ -1632,50 +1632,50 @@
       <c r="BK5" s="22"/>
     </row>
     <row r="6" spans="1:63" s="3" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
-      <c r="P6" s="68"/>
-      <c r="Q6" s="68"/>
-      <c r="R6" s="68"/>
-      <c r="S6" s="68"/>
-      <c r="T6" s="69"/>
-      <c r="U6" s="67" t="s">
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="32"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="32"/>
+      <c r="R6" s="32"/>
+      <c r="S6" s="32"/>
+      <c r="T6" s="33"/>
+      <c r="U6" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="68"/>
-      <c r="W6" s="68"/>
-      <c r="X6" s="68"/>
-      <c r="Y6" s="68"/>
-      <c r="Z6" s="68"/>
-      <c r="AA6" s="68"/>
-      <c r="AB6" s="69"/>
-      <c r="AC6" s="67"/>
-      <c r="AD6" s="68"/>
-      <c r="AE6" s="68"/>
-      <c r="AF6" s="68"/>
-      <c r="AG6" s="68"/>
-      <c r="AH6" s="68"/>
-      <c r="AI6" s="68"/>
-      <c r="AJ6" s="68"/>
-      <c r="AK6" s="68"/>
-      <c r="AL6" s="68"/>
-      <c r="AM6" s="68"/>
-      <c r="AN6" s="69"/>
+      <c r="V6" s="32"/>
+      <c r="W6" s="32"/>
+      <c r="X6" s="32"/>
+      <c r="Y6" s="32"/>
+      <c r="Z6" s="32"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="33"/>
+      <c r="AC6" s="31"/>
+      <c r="AD6" s="32"/>
+      <c r="AE6" s="32"/>
+      <c r="AF6" s="32"/>
+      <c r="AG6" s="32"/>
+      <c r="AH6" s="32"/>
+      <c r="AI6" s="32"/>
+      <c r="AJ6" s="32"/>
+      <c r="AK6" s="32"/>
+      <c r="AL6" s="32"/>
+      <c r="AM6" s="32"/>
+      <c r="AN6" s="33"/>
       <c r="AO6" s="6"/>
       <c r="AP6" s="6"/>
       <c r="AQ6" s="6"/>
@@ -1766,529 +1766,496 @@
       <c r="BK7" s="22"/>
     </row>
     <row r="8" spans="1:63" s="4" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38" t="s">
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38" t="s">
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="38" t="s">
+      <c r="J8" s="58"/>
+      <c r="K8" s="58"/>
+      <c r="L8" s="58"/>
+      <c r="M8" s="58"/>
+      <c r="N8" s="58"/>
+      <c r="O8" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="38"/>
-      <c r="R8" s="38"/>
-      <c r="S8" s="38"/>
-      <c r="T8" s="49"/>
-      <c r="U8" s="45" t="s">
+      <c r="P8" s="58"/>
+      <c r="Q8" s="58"/>
+      <c r="R8" s="58"/>
+      <c r="S8" s="58"/>
+      <c r="T8" s="59"/>
+      <c r="U8" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="V8" s="38"/>
-      <c r="W8" s="38"/>
-      <c r="X8" s="38" t="s">
+      <c r="V8" s="58"/>
+      <c r="W8" s="58"/>
+      <c r="X8" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="Y8" s="38"/>
-      <c r="Z8" s="38"/>
-      <c r="AA8" s="38"/>
-      <c r="AB8" s="38"/>
-      <c r="AC8" s="38" t="s">
+      <c r="Y8" s="58"/>
+      <c r="Z8" s="58"/>
+      <c r="AA8" s="58"/>
+      <c r="AB8" s="58"/>
+      <c r="AC8" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="AD8" s="38"/>
-      <c r="AE8" s="38"/>
-      <c r="AF8" s="38"/>
-      <c r="AG8" s="38"/>
-      <c r="AH8" s="38"/>
-      <c r="AI8" s="38" t="s">
+      <c r="AD8" s="58"/>
+      <c r="AE8" s="58"/>
+      <c r="AF8" s="58"/>
+      <c r="AG8" s="58"/>
+      <c r="AH8" s="58"/>
+      <c r="AI8" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="AJ8" s="38"/>
-      <c r="AK8" s="38"/>
-      <c r="AL8" s="38"/>
-      <c r="AM8" s="38"/>
-      <c r="AN8" s="38"/>
+      <c r="AJ8" s="58"/>
+      <c r="AK8" s="58"/>
+      <c r="AL8" s="58"/>
+      <c r="AM8" s="58"/>
+      <c r="AN8" s="58"/>
       <c r="AO8" s="5"/>
-      <c r="AP8" s="50"/>
-      <c r="AQ8" s="50"/>
-      <c r="AR8" s="50"/>
-      <c r="AS8" s="50"/>
-      <c r="AT8" s="50"/>
-      <c r="AU8" s="50"/>
-      <c r="AV8" s="50"/>
-      <c r="AW8" s="50"/>
+      <c r="AP8" s="34"/>
+      <c r="AQ8" s="34"/>
+      <c r="AR8" s="34"/>
+      <c r="AS8" s="34"/>
+      <c r="AT8" s="34"/>
+      <c r="AU8" s="34"/>
+      <c r="AV8" s="34"/>
+      <c r="AW8" s="34"/>
       <c r="AX8" s="23"/>
       <c r="AY8" s="23"/>
-      <c r="AZ8" s="48"/>
-      <c r="BA8" s="48"/>
-      <c r="BB8" s="48"/>
-      <c r="BC8" s="48"/>
+      <c r="AZ8" s="30"/>
+      <c r="BA8" s="30"/>
+      <c r="BB8" s="30"/>
+      <c r="BC8" s="30"/>
       <c r="BD8" s="24"/>
-      <c r="BE8" s="48"/>
-      <c r="BF8" s="48"/>
-      <c r="BG8" s="48"/>
-      <c r="BH8" s="48"/>
+      <c r="BE8" s="30"/>
+      <c r="BF8" s="30"/>
+      <c r="BG8" s="30"/>
+      <c r="BH8" s="30"/>
       <c r="BI8" s="24"/>
       <c r="BJ8" s="25"/>
       <c r="BK8" s="25"/>
     </row>
     <row r="9" spans="1:63" s="4" customFormat="1" ht="27" customHeight="1" thickTop="1">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="56"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="52"/>
-      <c r="K9" s="52"/>
-      <c r="L9" s="52"/>
-      <c r="M9" s="52"/>
-      <c r="N9" s="52"/>
-      <c r="O9" s="51"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="51"/>
-      <c r="R9" s="51"/>
-      <c r="S9" s="51"/>
-      <c r="T9" s="54"/>
-      <c r="U9" s="43" t="s">
+      <c r="B9" s="60"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="43"/>
+      <c r="N9" s="43"/>
+      <c r="O9" s="61"/>
+      <c r="P9" s="61"/>
+      <c r="Q9" s="61"/>
+      <c r="R9" s="61"/>
+      <c r="S9" s="61"/>
+      <c r="T9" s="62"/>
+      <c r="U9" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="V9" s="44"/>
-      <c r="W9" s="44"/>
-      <c r="X9" s="37"/>
-      <c r="Y9" s="37"/>
-      <c r="Z9" s="37"/>
-      <c r="AA9" s="37"/>
-      <c r="AB9" s="37"/>
-      <c r="AC9" s="52"/>
-      <c r="AD9" s="52"/>
-      <c r="AE9" s="52"/>
-      <c r="AF9" s="52"/>
-      <c r="AG9" s="52"/>
-      <c r="AH9" s="52"/>
-      <c r="AI9" s="51">
-        <f>O14+X9-AC9</f>
-        <v>0</v>
-      </c>
-      <c r="AJ9" s="51"/>
-      <c r="AK9" s="51"/>
-      <c r="AL9" s="51"/>
-      <c r="AM9" s="51"/>
-      <c r="AN9" s="51"/>
+      <c r="V9" s="60"/>
+      <c r="W9" s="60"/>
+      <c r="X9" s="72"/>
+      <c r="Y9" s="72"/>
+      <c r="Z9" s="72"/>
+      <c r="AA9" s="72"/>
+      <c r="AB9" s="72"/>
+      <c r="AC9" s="43"/>
+      <c r="AD9" s="43"/>
+      <c r="AE9" s="43"/>
+      <c r="AF9" s="43"/>
+      <c r="AG9" s="43"/>
+      <c r="AH9" s="43"/>
+      <c r="AI9" s="61"/>
+      <c r="AJ9" s="61"/>
+      <c r="AK9" s="61"/>
+      <c r="AL9" s="61"/>
+      <c r="AM9" s="61"/>
+      <c r="AN9" s="61"/>
       <c r="AO9" s="5"/>
-      <c r="AP9" s="50"/>
-      <c r="AQ9" s="50"/>
-      <c r="AR9" s="50"/>
-      <c r="AS9" s="50"/>
-      <c r="AT9" s="50"/>
-      <c r="AU9" s="50"/>
-      <c r="AV9" s="50"/>
-      <c r="AW9" s="50"/>
+      <c r="AP9" s="34"/>
+      <c r="AQ9" s="34"/>
+      <c r="AR9" s="34"/>
+      <c r="AS9" s="34"/>
+      <c r="AT9" s="34"/>
+      <c r="AU9" s="34"/>
+      <c r="AV9" s="34"/>
+      <c r="AW9" s="34"/>
       <c r="AX9" s="23"/>
       <c r="AY9" s="23"/>
-      <c r="AZ9" s="48"/>
-      <c r="BA9" s="48"/>
-      <c r="BB9" s="48"/>
-      <c r="BC9" s="48"/>
+      <c r="AZ9" s="30"/>
+      <c r="BA9" s="30"/>
+      <c r="BB9" s="30"/>
+      <c r="BC9" s="30"/>
       <c r="BD9" s="24"/>
-      <c r="BE9" s="48"/>
-      <c r="BF9" s="48"/>
-      <c r="BG9" s="48"/>
-      <c r="BH9" s="48"/>
+      <c r="BE9" s="30"/>
+      <c r="BF9" s="30"/>
+      <c r="BG9" s="30"/>
+      <c r="BH9" s="30"/>
       <c r="BI9" s="24"/>
       <c r="BJ9" s="25"/>
       <c r="BK9" s="25"/>
     </row>
     <row r="10" spans="1:63" s="4" customFormat="1" ht="27" customHeight="1">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="47"/>
-      <c r="L10" s="47"/>
-      <c r="M10" s="47"/>
-      <c r="N10" s="47"/>
-      <c r="O10" s="46">
-        <f>O9+D10-I10</f>
-        <v>0</v>
-      </c>
-      <c r="P10" s="46"/>
-      <c r="Q10" s="46"/>
-      <c r="R10" s="46"/>
-      <c r="S10" s="46"/>
-      <c r="T10" s="53"/>
-      <c r="U10" s="41" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="42"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="28"/>
+      <c r="S10" s="28"/>
+      <c r="T10" s="56"/>
+      <c r="U10" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="V10" s="42"/>
-      <c r="W10" s="42"/>
-      <c r="X10" s="36"/>
-      <c r="Y10" s="36"/>
-      <c r="Z10" s="36"/>
-      <c r="AA10" s="36"/>
-      <c r="AB10" s="36"/>
-      <c r="AC10" s="47"/>
-      <c r="AD10" s="47"/>
-      <c r="AE10" s="47"/>
-      <c r="AF10" s="47"/>
-      <c r="AG10" s="47"/>
-      <c r="AH10" s="47"/>
-      <c r="AI10" s="46">
-        <f>AI9+X10-AC10</f>
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="46"/>
-      <c r="AK10" s="46"/>
-      <c r="AL10" s="46"/>
-      <c r="AM10" s="46"/>
-      <c r="AN10" s="46"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="27"/>
+      <c r="X10" s="57"/>
+      <c r="Y10" s="57"/>
+      <c r="Z10" s="57"/>
+      <c r="AA10" s="57"/>
+      <c r="AB10" s="57"/>
+      <c r="AC10" s="42"/>
+      <c r="AD10" s="42"/>
+      <c r="AE10" s="42"/>
+      <c r="AF10" s="42"/>
+      <c r="AG10" s="42"/>
+      <c r="AH10" s="42"/>
+      <c r="AI10" s="28"/>
+      <c r="AJ10" s="28"/>
+      <c r="AK10" s="28"/>
+      <c r="AL10" s="28"/>
+      <c r="AM10" s="28"/>
+      <c r="AN10" s="28"/>
       <c r="AO10" s="5"/>
-      <c r="AP10" s="50"/>
-      <c r="AQ10" s="50"/>
-      <c r="AR10" s="50"/>
-      <c r="AS10" s="50"/>
-      <c r="AT10" s="50"/>
-      <c r="AU10" s="50"/>
-      <c r="AV10" s="50"/>
-      <c r="AW10" s="50"/>
+      <c r="AP10" s="34"/>
+      <c r="AQ10" s="34"/>
+      <c r="AR10" s="34"/>
+      <c r="AS10" s="34"/>
+      <c r="AT10" s="34"/>
+      <c r="AU10" s="34"/>
+      <c r="AV10" s="34"/>
+      <c r="AW10" s="34"/>
       <c r="AX10" s="23"/>
       <c r="AY10" s="23"/>
-      <c r="AZ10" s="48"/>
-      <c r="BA10" s="48"/>
-      <c r="BB10" s="48"/>
-      <c r="BC10" s="48"/>
+      <c r="AZ10" s="30"/>
+      <c r="BA10" s="30"/>
+      <c r="BB10" s="30"/>
+      <c r="BC10" s="30"/>
       <c r="BD10" s="24"/>
-      <c r="BE10" s="48"/>
-      <c r="BF10" s="48"/>
-      <c r="BG10" s="48"/>
-      <c r="BH10" s="48"/>
+      <c r="BE10" s="30"/>
+      <c r="BF10" s="30"/>
+      <c r="BG10" s="30"/>
+      <c r="BH10" s="30"/>
       <c r="BI10" s="24"/>
       <c r="BJ10" s="25"/>
       <c r="BK10" s="25"/>
     </row>
     <row r="11" spans="1:63" s="4" customFormat="1" ht="27" customHeight="1">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="47"/>
-      <c r="K11" s="47"/>
-      <c r="L11" s="47"/>
-      <c r="M11" s="47"/>
-      <c r="N11" s="47"/>
-      <c r="O11" s="46">
-        <f>O10+D11-I11</f>
-        <v>0</v>
-      </c>
-      <c r="P11" s="46"/>
-      <c r="Q11" s="46"/>
-      <c r="R11" s="46"/>
-      <c r="S11" s="46"/>
-      <c r="T11" s="53"/>
-      <c r="U11" s="41" t="s">
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="42"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28"/>
+      <c r="Q11" s="28"/>
+      <c r="R11" s="28"/>
+      <c r="S11" s="28"/>
+      <c r="T11" s="56"/>
+      <c r="U11" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="V11" s="42"/>
-      <c r="W11" s="42"/>
-      <c r="X11" s="36"/>
-      <c r="Y11" s="36"/>
-      <c r="Z11" s="36"/>
-      <c r="AA11" s="36"/>
-      <c r="AB11" s="36"/>
-      <c r="AC11" s="47"/>
-      <c r="AD11" s="47"/>
-      <c r="AE11" s="47"/>
-      <c r="AF11" s="47"/>
-      <c r="AG11" s="47"/>
-      <c r="AH11" s="47"/>
-      <c r="AI11" s="46">
-        <f>AI10+X11-AC11</f>
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="46"/>
-      <c r="AK11" s="46"/>
-      <c r="AL11" s="46"/>
-      <c r="AM11" s="46"/>
-      <c r="AN11" s="46"/>
+      <c r="V11" s="27"/>
+      <c r="W11" s="27"/>
+      <c r="X11" s="57"/>
+      <c r="Y11" s="57"/>
+      <c r="Z11" s="57"/>
+      <c r="AA11" s="57"/>
+      <c r="AB11" s="57"/>
+      <c r="AC11" s="42"/>
+      <c r="AD11" s="42"/>
+      <c r="AE11" s="42"/>
+      <c r="AF11" s="42"/>
+      <c r="AG11" s="42"/>
+      <c r="AH11" s="42"/>
+      <c r="AI11" s="28"/>
+      <c r="AJ11" s="28"/>
+      <c r="AK11" s="28"/>
+      <c r="AL11" s="28"/>
+      <c r="AM11" s="28"/>
+      <c r="AN11" s="28"/>
       <c r="AO11" s="5"/>
-      <c r="AP11" s="50"/>
-      <c r="AQ11" s="50"/>
-      <c r="AR11" s="50"/>
-      <c r="AS11" s="50"/>
-      <c r="AT11" s="50"/>
-      <c r="AU11" s="50"/>
-      <c r="AV11" s="50"/>
-      <c r="AW11" s="50"/>
+      <c r="AP11" s="34"/>
+      <c r="AQ11" s="34"/>
+      <c r="AR11" s="34"/>
+      <c r="AS11" s="34"/>
+      <c r="AT11" s="34"/>
+      <c r="AU11" s="34"/>
+      <c r="AV11" s="34"/>
+      <c r="AW11" s="34"/>
       <c r="AX11" s="23"/>
       <c r="AY11" s="23"/>
-      <c r="AZ11" s="48"/>
-      <c r="BA11" s="48"/>
-      <c r="BB11" s="48"/>
-      <c r="BC11" s="48"/>
+      <c r="AZ11" s="30"/>
+      <c r="BA11" s="30"/>
+      <c r="BB11" s="30"/>
+      <c r="BC11" s="30"/>
       <c r="BD11" s="24"/>
-      <c r="BE11" s="48"/>
-      <c r="BF11" s="48"/>
-      <c r="BG11" s="48"/>
-      <c r="BH11" s="48"/>
+      <c r="BE11" s="30"/>
+      <c r="BF11" s="30"/>
+      <c r="BG11" s="30"/>
+      <c r="BH11" s="30"/>
       <c r="BI11" s="24"/>
       <c r="BJ11" s="25"/>
       <c r="BK11" s="25"/>
     </row>
     <row r="12" spans="1:63" s="4" customFormat="1" ht="27" customHeight="1">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="47"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="47"/>
-      <c r="O12" s="46">
-        <f>O11+D12-I12</f>
-        <v>0</v>
-      </c>
-      <c r="P12" s="46"/>
-      <c r="Q12" s="46"/>
-      <c r="R12" s="46"/>
-      <c r="S12" s="46"/>
-      <c r="T12" s="53"/>
-      <c r="U12" s="41" t="s">
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="42"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="28"/>
+      <c r="T12" s="56"/>
+      <c r="U12" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="V12" s="42"/>
-      <c r="W12" s="42"/>
-      <c r="X12" s="36"/>
-      <c r="Y12" s="36"/>
-      <c r="Z12" s="36"/>
-      <c r="AA12" s="36"/>
-      <c r="AB12" s="36"/>
-      <c r="AC12" s="47"/>
-      <c r="AD12" s="47"/>
-      <c r="AE12" s="47"/>
-      <c r="AF12" s="47"/>
-      <c r="AG12" s="47"/>
-      <c r="AH12" s="47"/>
-      <c r="AI12" s="46">
-        <f>AI11+X12-AC12</f>
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="46"/>
-      <c r="AK12" s="46"/>
-      <c r="AL12" s="46"/>
-      <c r="AM12" s="46"/>
-      <c r="AN12" s="46"/>
+      <c r="V12" s="27"/>
+      <c r="W12" s="27"/>
+      <c r="X12" s="57"/>
+      <c r="Y12" s="57"/>
+      <c r="Z12" s="57"/>
+      <c r="AA12" s="57"/>
+      <c r="AB12" s="57"/>
+      <c r="AC12" s="42"/>
+      <c r="AD12" s="42"/>
+      <c r="AE12" s="42"/>
+      <c r="AF12" s="42"/>
+      <c r="AG12" s="42"/>
+      <c r="AH12" s="42"/>
+      <c r="AI12" s="28"/>
+      <c r="AJ12" s="28"/>
+      <c r="AK12" s="28"/>
+      <c r="AL12" s="28"/>
+      <c r="AM12" s="28"/>
+      <c r="AN12" s="28"/>
       <c r="AO12" s="5"/>
-      <c r="AP12" s="50"/>
-      <c r="AQ12" s="50"/>
-      <c r="AR12" s="50"/>
-      <c r="AS12" s="50"/>
-      <c r="AT12" s="50"/>
-      <c r="AU12" s="50"/>
-      <c r="AV12" s="50"/>
-      <c r="AW12" s="50"/>
+      <c r="AP12" s="34"/>
+      <c r="AQ12" s="34"/>
+      <c r="AR12" s="34"/>
+      <c r="AS12" s="34"/>
+      <c r="AT12" s="34"/>
+      <c r="AU12" s="34"/>
+      <c r="AV12" s="34"/>
+      <c r="AW12" s="34"/>
       <c r="AX12" s="23"/>
       <c r="AY12" s="23"/>
-      <c r="AZ12" s="48"/>
-      <c r="BA12" s="48"/>
-      <c r="BB12" s="48"/>
-      <c r="BC12" s="48"/>
+      <c r="AZ12" s="30"/>
+      <c r="BA12" s="30"/>
+      <c r="BB12" s="30"/>
+      <c r="BC12" s="30"/>
       <c r="BD12" s="24"/>
-      <c r="BE12" s="48"/>
-      <c r="BF12" s="48"/>
-      <c r="BG12" s="48"/>
-      <c r="BH12" s="48"/>
+      <c r="BE12" s="30"/>
+      <c r="BF12" s="30"/>
+      <c r="BG12" s="30"/>
+      <c r="BH12" s="30"/>
       <c r="BI12" s="24"/>
       <c r="BJ12" s="25"/>
       <c r="BK12" s="25"/>
     </row>
     <row r="13" spans="1:63" s="4" customFormat="1" ht="27" customHeight="1">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="47"/>
-      <c r="K13" s="47"/>
-      <c r="L13" s="47"/>
-      <c r="M13" s="47"/>
-      <c r="N13" s="47"/>
-      <c r="O13" s="46">
-        <f>O12+D13-I13</f>
-        <v>0</v>
-      </c>
-      <c r="P13" s="46"/>
-      <c r="Q13" s="46"/>
-      <c r="R13" s="46"/>
-      <c r="S13" s="46"/>
-      <c r="T13" s="53"/>
-      <c r="U13" s="41" t="s">
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="28"/>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="28"/>
+      <c r="S13" s="28"/>
+      <c r="T13" s="56"/>
+      <c r="U13" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="V13" s="42"/>
-      <c r="W13" s="42"/>
-      <c r="X13" s="36"/>
-      <c r="Y13" s="36"/>
-      <c r="Z13" s="36"/>
-      <c r="AA13" s="36"/>
-      <c r="AB13" s="36"/>
-      <c r="AC13" s="47"/>
-      <c r="AD13" s="47"/>
-      <c r="AE13" s="47"/>
-      <c r="AF13" s="47"/>
-      <c r="AG13" s="47"/>
-      <c r="AH13" s="47"/>
-      <c r="AI13" s="46">
-        <f>AI12+X13-AC13</f>
-        <v>0</v>
-      </c>
-      <c r="AJ13" s="46"/>
-      <c r="AK13" s="46"/>
-      <c r="AL13" s="46"/>
-      <c r="AM13" s="46"/>
-      <c r="AN13" s="46"/>
+      <c r="V13" s="27"/>
+      <c r="W13" s="27"/>
+      <c r="X13" s="57"/>
+      <c r="Y13" s="57"/>
+      <c r="Z13" s="57"/>
+      <c r="AA13" s="57"/>
+      <c r="AB13" s="57"/>
+      <c r="AC13" s="42"/>
+      <c r="AD13" s="42"/>
+      <c r="AE13" s="42"/>
+      <c r="AF13" s="42"/>
+      <c r="AG13" s="42"/>
+      <c r="AH13" s="42"/>
+      <c r="AI13" s="28"/>
+      <c r="AJ13" s="28"/>
+      <c r="AK13" s="28"/>
+      <c r="AL13" s="28"/>
+      <c r="AM13" s="28"/>
+      <c r="AN13" s="28"/>
       <c r="AO13" s="5"/>
-      <c r="AP13" s="50"/>
-      <c r="AQ13" s="50"/>
-      <c r="AR13" s="50"/>
-      <c r="AS13" s="50"/>
-      <c r="AT13" s="50"/>
-      <c r="AU13" s="50"/>
-      <c r="AV13" s="50"/>
-      <c r="AW13" s="50"/>
+      <c r="AP13" s="34"/>
+      <c r="AQ13" s="34"/>
+      <c r="AR13" s="34"/>
+      <c r="AS13" s="34"/>
+      <c r="AT13" s="34"/>
+      <c r="AU13" s="34"/>
+      <c r="AV13" s="34"/>
+      <c r="AW13" s="34"/>
       <c r="AX13" s="23"/>
       <c r="AY13" s="23"/>
-      <c r="AZ13" s="48"/>
-      <c r="BA13" s="48"/>
-      <c r="BB13" s="48"/>
-      <c r="BC13" s="48"/>
+      <c r="AZ13" s="30"/>
+      <c r="BA13" s="30"/>
+      <c r="BB13" s="30"/>
+      <c r="BC13" s="30"/>
       <c r="BD13" s="24"/>
-      <c r="BE13" s="48"/>
-      <c r="BF13" s="48"/>
-      <c r="BG13" s="48"/>
-      <c r="BH13" s="48"/>
+      <c r="BE13" s="30"/>
+      <c r="BF13" s="30"/>
+      <c r="BG13" s="30"/>
+      <c r="BH13" s="30"/>
       <c r="BI13" s="24"/>
       <c r="BJ13" s="25"/>
       <c r="BK13" s="25"/>
     </row>
     <row r="14" spans="1:63" s="4" customFormat="1" ht="27" customHeight="1">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="47"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="47"/>
-      <c r="N14" s="47"/>
-      <c r="O14" s="46">
-        <f>O13+D14-I14</f>
-        <v>0</v>
-      </c>
-      <c r="P14" s="46"/>
-      <c r="Q14" s="46"/>
-      <c r="R14" s="46"/>
-      <c r="S14" s="46"/>
-      <c r="T14" s="53"/>
-      <c r="U14" s="41" t="s">
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="42"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="28"/>
+      <c r="Q14" s="28"/>
+      <c r="R14" s="28"/>
+      <c r="S14" s="28"/>
+      <c r="T14" s="56"/>
+      <c r="U14" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="V14" s="42"/>
-      <c r="W14" s="42"/>
-      <c r="X14" s="36"/>
-      <c r="Y14" s="36"/>
-      <c r="Z14" s="36"/>
-      <c r="AA14" s="36"/>
-      <c r="AB14" s="36"/>
-      <c r="AC14" s="47"/>
-      <c r="AD14" s="47"/>
-      <c r="AE14" s="47"/>
-      <c r="AF14" s="47"/>
-      <c r="AG14" s="47"/>
-      <c r="AH14" s="47"/>
-      <c r="AI14" s="46">
-        <f>AI13+X14-AC14</f>
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="46"/>
-      <c r="AK14" s="46"/>
-      <c r="AL14" s="46"/>
-      <c r="AM14" s="46"/>
-      <c r="AN14" s="46"/>
+      <c r="V14" s="27"/>
+      <c r="W14" s="27"/>
+      <c r="X14" s="57"/>
+      <c r="Y14" s="57"/>
+      <c r="Z14" s="57"/>
+      <c r="AA14" s="57"/>
+      <c r="AB14" s="57"/>
+      <c r="AC14" s="42"/>
+      <c r="AD14" s="42"/>
+      <c r="AE14" s="42"/>
+      <c r="AF14" s="42"/>
+      <c r="AG14" s="42"/>
+      <c r="AH14" s="42"/>
+      <c r="AI14" s="28"/>
+      <c r="AJ14" s="28"/>
+      <c r="AK14" s="28"/>
+      <c r="AL14" s="28"/>
+      <c r="AM14" s="28"/>
+      <c r="AN14" s="28"/>
       <c r="AO14" s="5"/>
-      <c r="AP14" s="50"/>
-      <c r="AQ14" s="50"/>
-      <c r="AR14" s="50"/>
-      <c r="AS14" s="50"/>
-      <c r="AT14" s="50"/>
-      <c r="AU14" s="50"/>
-      <c r="AV14" s="50"/>
-      <c r="AW14" s="50"/>
+      <c r="AP14" s="34"/>
+      <c r="AQ14" s="34"/>
+      <c r="AR14" s="34"/>
+      <c r="AS14" s="34"/>
+      <c r="AT14" s="34"/>
+      <c r="AU14" s="34"/>
+      <c r="AV14" s="34"/>
+      <c r="AW14" s="34"/>
       <c r="AX14" s="23"/>
       <c r="AY14" s="23"/>
-      <c r="AZ14" s="48"/>
-      <c r="BA14" s="48"/>
-      <c r="BB14" s="48"/>
-      <c r="BC14" s="48"/>
+      <c r="AZ14" s="30"/>
+      <c r="BA14" s="30"/>
+      <c r="BB14" s="30"/>
+      <c r="BC14" s="30"/>
       <c r="BD14" s="24"/>
-      <c r="BE14" s="48"/>
-      <c r="BF14" s="48"/>
-      <c r="BG14" s="48"/>
-      <c r="BH14" s="48"/>
+      <c r="BE14" s="30"/>
+      <c r="BF14" s="30"/>
+      <c r="BG14" s="30"/>
+      <c r="BH14" s="30"/>
       <c r="BI14" s="24"/>
       <c r="BJ14" s="25"/>
       <c r="BK14" s="25"/>
@@ -2314,32 +2281,32 @@
       <c r="R15" s="19"/>
       <c r="S15" s="19"/>
       <c r="T15" s="19"/>
-      <c r="U15" s="39"/>
-      <c r="V15" s="40"/>
-      <c r="W15" s="40"/>
-      <c r="X15" s="77">
+      <c r="U15" s="73"/>
+      <c r="V15" s="74"/>
+      <c r="W15" s="74"/>
+      <c r="X15" s="38">
         <f>SUM(D9:H14,X9:AB14)</f>
         <v>0</v>
       </c>
-      <c r="Y15" s="77"/>
-      <c r="Z15" s="77"/>
-      <c r="AA15" s="77"/>
-      <c r="AB15" s="77"/>
-      <c r="AC15" s="75">
+      <c r="Y15" s="38"/>
+      <c r="Z15" s="38"/>
+      <c r="AA15" s="38"/>
+      <c r="AB15" s="38"/>
+      <c r="AC15" s="36">
         <f>SUM(I9:N14,AC9:AH14)</f>
         <v>0</v>
       </c>
-      <c r="AD15" s="75"/>
-      <c r="AE15" s="75"/>
-      <c r="AF15" s="75"/>
-      <c r="AG15" s="75"/>
-      <c r="AH15" s="75"/>
-      <c r="AI15" s="76"/>
-      <c r="AJ15" s="76"/>
-      <c r="AK15" s="76"/>
-      <c r="AL15" s="76"/>
-      <c r="AM15" s="76"/>
-      <c r="AN15" s="76"/>
+      <c r="AD15" s="36"/>
+      <c r="AE15" s="36"/>
+      <c r="AF15" s="36"/>
+      <c r="AG15" s="36"/>
+      <c r="AH15" s="36"/>
+      <c r="AI15" s="37"/>
+      <c r="AJ15" s="37"/>
+      <c r="AK15" s="37"/>
+      <c r="AL15" s="37"/>
+      <c r="AM15" s="37"/>
+      <c r="AN15" s="37"/>
       <c r="AO15" s="5"/>
       <c r="AP15" s="15"/>
       <c r="AQ15" s="15"/>
@@ -2456,103 +2423,197 @@
       <c r="BK17" s="26"/>
     </row>
     <row r="18" spans="1:63" ht="27" customHeight="1">
-      <c r="A18" s="73" t="s">
+      <c r="A18" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="73"/>
-      <c r="C18" s="73"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="74" t="s">
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="74"/>
-      <c r="G18" s="74"/>
-      <c r="H18" s="74"/>
-      <c r="I18" s="74"/>
-      <c r="J18" s="74"/>
-      <c r="K18" s="74"/>
-      <c r="L18" s="74"/>
-      <c r="M18" s="74" t="s">
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="N18" s="74"/>
-      <c r="O18" s="74"/>
-      <c r="P18" s="74"/>
-      <c r="Q18" s="74"/>
-      <c r="R18" s="74"/>
-      <c r="S18" s="74"/>
-      <c r="T18" s="74"/>
-      <c r="U18" s="73" t="s">
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="35"/>
+      <c r="T18" s="35"/>
+      <c r="U18" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="V18" s="73"/>
-      <c r="W18" s="73"/>
-      <c r="X18" s="73"/>
-      <c r="Y18" s="73"/>
-      <c r="Z18" s="73"/>
-      <c r="AA18" s="73"/>
-      <c r="AB18" s="73"/>
-      <c r="AC18" s="30" t="s">
+      <c r="V18" s="29"/>
+      <c r="W18" s="29"/>
+      <c r="X18" s="29"/>
+      <c r="Y18" s="29"/>
+      <c r="Z18" s="29"/>
+      <c r="AA18" s="29"/>
+      <c r="AB18" s="29"/>
+      <c r="AC18" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="AD18" s="31"/>
-      <c r="AE18" s="31"/>
-      <c r="AF18" s="31"/>
-      <c r="AG18" s="31"/>
-      <c r="AH18" s="32"/>
-      <c r="AI18" s="30" t="s">
+      <c r="AD18" s="67"/>
+      <c r="AE18" s="67"/>
+      <c r="AF18" s="67"/>
+      <c r="AG18" s="67"/>
+      <c r="AH18" s="68"/>
+      <c r="AI18" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="AJ18" s="31"/>
-      <c r="AK18" s="31"/>
-      <c r="AL18" s="31"/>
-      <c r="AM18" s="31"/>
-      <c r="AN18" s="32"/>
+      <c r="AJ18" s="67"/>
+      <c r="AK18" s="67"/>
+      <c r="AL18" s="67"/>
+      <c r="AM18" s="67"/>
+      <c r="AN18" s="68"/>
     </row>
     <row r="19" spans="1:63" ht="27" customHeight="1">
-      <c r="A19" s="42"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="46"/>
-      <c r="M19" s="46"/>
-      <c r="N19" s="46"/>
-      <c r="O19" s="46"/>
-      <c r="P19" s="46"/>
-      <c r="Q19" s="46"/>
-      <c r="R19" s="46"/>
-      <c r="S19" s="46"/>
-      <c r="T19" s="46"/>
-      <c r="U19" s="46"/>
-      <c r="V19" s="42"/>
-      <c r="W19" s="42"/>
-      <c r="X19" s="42"/>
-      <c r="Y19" s="42"/>
-      <c r="Z19" s="42"/>
-      <c r="AA19" s="42"/>
-      <c r="AB19" s="42"/>
-      <c r="AC19" s="27"/>
-      <c r="AD19" s="28"/>
-      <c r="AE19" s="28"/>
-      <c r="AF19" s="28"/>
-      <c r="AG19" s="28"/>
-      <c r="AH19" s="29"/>
-      <c r="AI19" s="33"/>
-      <c r="AJ19" s="34"/>
-      <c r="AK19" s="34"/>
-      <c r="AL19" s="34"/>
-      <c r="AM19" s="34"/>
-      <c r="AN19" s="35"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="28"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="28"/>
+      <c r="T19" s="28"/>
+      <c r="U19" s="28"/>
+      <c r="V19" s="27"/>
+      <c r="W19" s="27"/>
+      <c r="X19" s="27"/>
+      <c r="Y19" s="27"/>
+      <c r="Z19" s="27"/>
+      <c r="AA19" s="27"/>
+      <c r="AB19" s="27"/>
+      <c r="AC19" s="63"/>
+      <c r="AD19" s="64"/>
+      <c r="AE19" s="64"/>
+      <c r="AF19" s="64"/>
+      <c r="AG19" s="64"/>
+      <c r="AH19" s="65"/>
+      <c r="AI19" s="69"/>
+      <c r="AJ19" s="70"/>
+      <c r="AK19" s="70"/>
+      <c r="AL19" s="70"/>
+      <c r="AM19" s="70"/>
+      <c r="AN19" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="118">
+    <mergeCell ref="AC19:AH19"/>
+    <mergeCell ref="AC18:AH18"/>
+    <mergeCell ref="AI19:AN19"/>
+    <mergeCell ref="AI18:AN18"/>
+    <mergeCell ref="X11:AB11"/>
+    <mergeCell ref="X10:AB10"/>
+    <mergeCell ref="X9:AB9"/>
+    <mergeCell ref="X8:AB8"/>
+    <mergeCell ref="U15:W15"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="U13:W13"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="U11:W11"/>
+    <mergeCell ref="U10:W10"/>
+    <mergeCell ref="U9:W9"/>
+    <mergeCell ref="U8:W8"/>
+    <mergeCell ref="AI12:AN12"/>
+    <mergeCell ref="AI11:AN11"/>
+    <mergeCell ref="AC14:AH14"/>
+    <mergeCell ref="BE8:BH8"/>
+    <mergeCell ref="I8:N8"/>
+    <mergeCell ref="AC8:AH8"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="O8:T8"/>
+    <mergeCell ref="AI8:AN8"/>
+    <mergeCell ref="AP8:AS8"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="AI10:AN10"/>
+    <mergeCell ref="AI9:AN9"/>
+    <mergeCell ref="AC13:AH13"/>
+    <mergeCell ref="AC12:AH12"/>
+    <mergeCell ref="AC11:AH11"/>
+    <mergeCell ref="AC10:AH10"/>
+    <mergeCell ref="AC9:AH9"/>
+    <mergeCell ref="O11:T11"/>
+    <mergeCell ref="O10:T10"/>
+    <mergeCell ref="O9:T9"/>
+    <mergeCell ref="I11:N11"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="AZ9:BC9"/>
+    <mergeCell ref="O14:T14"/>
+    <mergeCell ref="O13:T13"/>
+    <mergeCell ref="O12:T12"/>
+    <mergeCell ref="X14:AB14"/>
+    <mergeCell ref="X13:AB13"/>
+    <mergeCell ref="X12:AB12"/>
+    <mergeCell ref="I14:N14"/>
+    <mergeCell ref="I13:N13"/>
+    <mergeCell ref="I12:N12"/>
+    <mergeCell ref="A2:Z3"/>
+    <mergeCell ref="AA2:AB3"/>
+    <mergeCell ref="AC2:AE2"/>
+    <mergeCell ref="AF2:AH2"/>
+    <mergeCell ref="AI2:AK2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="AC3:AE3"/>
+    <mergeCell ref="AF3:AH3"/>
+    <mergeCell ref="AI3:AK3"/>
+    <mergeCell ref="AL3:AN3"/>
+    <mergeCell ref="AC6:AN6"/>
+    <mergeCell ref="AC5:AN5"/>
+    <mergeCell ref="I5:T5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="I6:T6"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="AT8:AW8"/>
+    <mergeCell ref="AZ8:BC8"/>
+    <mergeCell ref="AZ10:BC10"/>
+    <mergeCell ref="I10:N10"/>
+    <mergeCell ref="I9:N9"/>
+    <mergeCell ref="BE10:BH10"/>
+    <mergeCell ref="AP14:AS14"/>
+    <mergeCell ref="AT14:AW14"/>
+    <mergeCell ref="AZ14:BC14"/>
+    <mergeCell ref="BE14:BH14"/>
+    <mergeCell ref="AP13:AS13"/>
+    <mergeCell ref="AT13:AW13"/>
+    <mergeCell ref="AZ13:BC13"/>
+    <mergeCell ref="BE13:BH13"/>
+    <mergeCell ref="AP12:AS12"/>
+    <mergeCell ref="AT12:AW12"/>
+    <mergeCell ref="AZ12:BC12"/>
+    <mergeCell ref="BE12:BH12"/>
+    <mergeCell ref="AP11:AS11"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="AI14:AN14"/>
     <mergeCell ref="AI13:AN13"/>
@@ -2577,100 +2638,6 @@
     <mergeCell ref="BE11:BH11"/>
     <mergeCell ref="AP10:AS10"/>
     <mergeCell ref="AT10:AW10"/>
-    <mergeCell ref="BE10:BH10"/>
-    <mergeCell ref="AP14:AS14"/>
-    <mergeCell ref="AT14:AW14"/>
-    <mergeCell ref="AZ14:BC14"/>
-    <mergeCell ref="BE14:BH14"/>
-    <mergeCell ref="AP13:AS13"/>
-    <mergeCell ref="AT13:AW13"/>
-    <mergeCell ref="AZ13:BC13"/>
-    <mergeCell ref="BE13:BH13"/>
-    <mergeCell ref="AP12:AS12"/>
-    <mergeCell ref="AT12:AW12"/>
-    <mergeCell ref="AZ12:BC12"/>
-    <mergeCell ref="BE12:BH12"/>
-    <mergeCell ref="AP11:AS11"/>
-    <mergeCell ref="AC6:AN6"/>
-    <mergeCell ref="AC5:AN5"/>
-    <mergeCell ref="I5:T5"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="I6:T6"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="AT8:AW8"/>
-    <mergeCell ref="AZ8:BC8"/>
-    <mergeCell ref="AZ10:BC10"/>
-    <mergeCell ref="I10:N10"/>
-    <mergeCell ref="I9:N9"/>
-    <mergeCell ref="A2:Z3"/>
-    <mergeCell ref="AA2:AB3"/>
-    <mergeCell ref="AC2:AE2"/>
-    <mergeCell ref="AF2:AH2"/>
-    <mergeCell ref="AI2:AK2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="AC3:AE3"/>
-    <mergeCell ref="AF3:AH3"/>
-    <mergeCell ref="AI3:AK3"/>
-    <mergeCell ref="AL3:AN3"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="AZ9:BC9"/>
-    <mergeCell ref="O14:T14"/>
-    <mergeCell ref="O13:T13"/>
-    <mergeCell ref="O12:T12"/>
-    <mergeCell ref="X14:AB14"/>
-    <mergeCell ref="X13:AB13"/>
-    <mergeCell ref="X12:AB12"/>
-    <mergeCell ref="I14:N14"/>
-    <mergeCell ref="I13:N13"/>
-    <mergeCell ref="I12:N12"/>
-    <mergeCell ref="BE8:BH8"/>
-    <mergeCell ref="I8:N8"/>
-    <mergeCell ref="AC8:AH8"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="O8:T8"/>
-    <mergeCell ref="AI8:AN8"/>
-    <mergeCell ref="AP8:AS8"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="AI10:AN10"/>
-    <mergeCell ref="AI9:AN9"/>
-    <mergeCell ref="AC13:AH13"/>
-    <mergeCell ref="AC12:AH12"/>
-    <mergeCell ref="AC11:AH11"/>
-    <mergeCell ref="AC10:AH10"/>
-    <mergeCell ref="AC9:AH9"/>
-    <mergeCell ref="O11:T11"/>
-    <mergeCell ref="O10:T10"/>
-    <mergeCell ref="O9:T9"/>
-    <mergeCell ref="I11:N11"/>
-    <mergeCell ref="AC19:AH19"/>
-    <mergeCell ref="AC18:AH18"/>
-    <mergeCell ref="AI19:AN19"/>
-    <mergeCell ref="AI18:AN18"/>
-    <mergeCell ref="X11:AB11"/>
-    <mergeCell ref="X10:AB10"/>
-    <mergeCell ref="X9:AB9"/>
-    <mergeCell ref="X8:AB8"/>
-    <mergeCell ref="U15:W15"/>
-    <mergeCell ref="U14:W14"/>
-    <mergeCell ref="U13:W13"/>
-    <mergeCell ref="U12:W12"/>
-    <mergeCell ref="U11:W11"/>
-    <mergeCell ref="U10:W10"/>
-    <mergeCell ref="U9:W9"/>
-    <mergeCell ref="U8:W8"/>
-    <mergeCell ref="AI12:AN12"/>
-    <mergeCell ref="AI11:AN11"/>
-    <mergeCell ref="AC14:AH14"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.78740157480314965" right="0.59055118110236227" top="0.98425196850393704" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
